--- a/dictionary/faz1_variable_dictionary.xlsx
+++ b/dictionary/faz1_variable_dictionary.xlsx
@@ -15,11 +15,11 @@
     <sheet name="Elenenler - Gerekce" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'29 Business Headings'!$A$1:$U$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'29 Business Headings'!$A$1:$V$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Faz1 Base (11)'!$A$1:$H$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Faz1 Derived (42)'!$A$1:$E$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Faz1 Native (23)'!$A$1:$E$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Elenenler - Gerekce'!$A$1:$D$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Elenenler - Gerekce'!$A$1:$E$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -74,7 +74,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -93,6 +93,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F4B084"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
@@ -103,12 +113,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7E6E6"/>
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -139,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -167,7 +177,13 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -182,13 +198,19 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -200,16 +222,15 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -575,11 +596,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -681,7 +702,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Leading + surekli numerik + genis uygulanabilir + rule/lagging/segment-specific degil</t>
+          <t>Leading + musterinin kendi + surekli numerik + genis uygulanabilir</t>
         </is>
       </c>
     </row>
@@ -693,7 +714,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>RULE (kural/esik), SEGMENT (dar portfoy), LAGGING (already-bad), AMBIGUOUS (belirsiz sinyal)</t>
+          <t>LAGGING_SELF, COUNTERPARTY, RULE, SEGMENT_SPECIFIC, NARROW_SCOPE, BIDIRECTIONAL_OR_JUDGMENT</t>
         </is>
       </c>
     </row>
@@ -724,79 +745,115 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>Monitor history tablo</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>EWS_TO_FAZ1_MONITOR_HISTORY (run bazli health metrikleri)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>Output tablo</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>EWS_TO_FAZ1_RESULTS / DETAILS / FEATURE_EFFECTS</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Renk Kodlari</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>FAZ1</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Faz 1 base setine alindi</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Faz 1 base setine alindi (11 degisken)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>LAGGING_SELF</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Musterinin kendi olumsuzluk olayi zaten gerceklesmis (haciz, gecikme, kredi karti, faktoring, forward check)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>COUNTERPARTY</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Musterinin kendi degil, karsi tarafinin (kesideci / alici / sigortali) olumsuzlugu</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>RULE</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Rule / kural / esik pattern'i - companion layer</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>SEGMENT</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Segment-specific (dar alt portfoy)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>LAGGING</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Lagging / already-bad (olay gerceklesmis)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Belirsiz yon veya dar sinyal</t>
+          <t>Tam pattern kurgusu; surekli oran/indikator yok, sadece deterministic event pattern'leri (ilk kez, pes pese, frekans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>SEGMENT_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Yalniz belirli NACE / alt portfoy icin tanimli</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>NARROW_SCOPE</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Metodoloji leading ama kapsam dar (sadece bankamiz, belli urun)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>BIDIRECTIONAL_OR_JUDGMENT</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Yon belirsiz veya standardize edilemeyen yargi metrigi</t>
         </is>
       </c>
     </row>
@@ -814,14 +871,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U30"/>
+  <dimension ref="A1:V30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="48" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
@@ -837,117 +894,123 @@
     <col width="45" customWidth="1" min="18" max="18"/>
     <col width="32" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="55" customWidth="1" min="21" max="21"/>
+    <col width="70" customWidth="1" min="21" max="21"/>
+    <col width="70" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Sayfa</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Business Basligi</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Canonical Name</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Portfolio Scope</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Model Placement</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Source / Accounts</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>Period / Annualization</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="13" t="inlineStr">
         <is>
           <t>Calculation Logic</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="13" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="M1" s="11" t="inlineStr">
+      <c r="M1" s="13" t="inlineStr">
         <is>
           <t>Refresh Frequency</t>
         </is>
       </c>
-      <c r="N1" s="11" t="inlineStr">
+      <c r="N1" s="13" t="inlineStr">
         <is>
           <t>Freshness Rule</t>
         </is>
       </c>
-      <c r="O1" s="11" t="inlineStr">
+      <c r="O1" s="13" t="inlineStr">
         <is>
           <t>Applicable Segments</t>
         </is>
       </c>
-      <c r="P1" s="11" t="inlineStr">
+      <c r="P1" s="13" t="inlineStr">
         <is>
           <t>Model Treatment</t>
         </is>
       </c>
-      <c r="Q1" s="11" t="inlineStr">
+      <c r="Q1" s="13" t="inlineStr">
         <is>
           <t>Companion Rules / Filters</t>
         </is>
       </c>
-      <c r="R1" s="11" t="inlineStr">
+      <c r="R1" s="13" t="inlineStr">
         <is>
           <t>Recommended History Features</t>
         </is>
       </c>
-      <c r="S1" s="11" t="inlineStr">
+      <c r="S1" s="13" t="inlineStr">
         <is>
           <t>Population Reference</t>
         </is>
       </c>
-      <c r="T1" s="11" t="inlineStr">
+      <c r="T1" s="13" t="inlineStr">
         <is>
           <t>Faz 1 Karari</t>
         </is>
       </c>
-      <c r="U1" s="11" t="inlineStr">
-        <is>
-          <t>Gerekce</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="60" customHeight="1">
+      <c r="U1" s="13" t="inlineStr">
+        <is>
+          <t>Kategori Gerekcesi</t>
+        </is>
+      </c>
+      <c r="V1" s="13" t="inlineStr">
+        <is>
+          <t>Secim Gerekcesi (Faz 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="80" customHeight="1">
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
@@ -964,7 +1027,7 @@
           <t>bank_debt_to_turnover</t>
         </is>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>FAZ1</t>
         </is>
@@ -1039,18 +1102,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T2" s="13" t="inlineStr">
+      <c r="T2" s="15" t="inlineStr">
         <is>
           <t>DAHIL</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>Leading; bilanco + memzuc kapsayici kaldirac sinyali</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
+          <t>Leading: musterinin kendi bilanco + Memzuc kaynagindan turetilmis surekli numerik oran.</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>Faz 1 'bilancolu + POS yogun Ticari Orta' kapsayici anomaly hedefinin merkezi kaldirac orani; kohortun tum uyelerine uygulanabilir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="80" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
@@ -1067,7 +1135,7 @@
           <t>pos_volume_change</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>FAZ1</t>
         </is>
@@ -1142,18 +1210,23 @@
           <t>yes (population_percentile, median_ratio)</t>
         </is>
       </c>
-      <c r="T3" s="13" t="inlineStr">
+      <c r="T3" s="15" t="inlineStr">
         <is>
           <t>DAHIL</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>Leading nakit akis proxy'si; cohort kriteri + population reference</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="60" customHeight="1">
+          <t>Leading: musterinin kendi nakit akis proxy'si; ay ay YoY degisim.</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>Cohort ikinci filtresi ('POS yogun') bu metrige gelir; mevsimsellik riskini population reference (percentile, median delta) ile hafifletiyoruz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="80" customHeight="1">
       <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
@@ -1170,9 +1243,9 @@
           <t>seizure_amount_to_turnover</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
-        <is>
-          <t>RULE</t>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>LAGGING_SELF</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -1245,18 +1318,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T4" s="15" t="inlineStr">
+      <c r="T4" s="17" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>Rule: 'son 2 yilda ilk kez haciz' pattern + lagging (haciz zaten var)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
+          <t>Musterinin kendi olumsuzlugu: devam eden haciz zaten yasanmis bir olay (self-lagging). Rule pattern'i 'ilk kez 24m' sadece companion filtredir.</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>Kapsayici erken uyari skoruna katkisi sinirli; olay gerceklestikten sonra sinyal uretir. Faz 2'de rule katmaninda kullanilacak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="80" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
@@ -1273,7 +1351,7 @@
           <t>check_payment_time_shift</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>RULE</t>
         </is>
@@ -1348,18 +1426,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T5" s="15" t="inlineStr">
+      <c r="T5" s="17" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>Rule: 'son 6 ayda ilk kez', 'son 3 ayda pes pese farkli gunler'</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
+          <t>Tam pattern kurgusu: 'son 6 ayda ilk kez ogleden sonra', 'son 3 ayda pes pese farkli gun'. Modele girecek surekli oran/indikator yok, sadece deterministic event pattern'leri.</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>Modelleme degiskeni olamaz (tek sayisi/orani yok); rule katmaninda companion olarak calisir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
       <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
@@ -1376,9 +1459,9 @@
           <t>factoring_risk_presence</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>RULE</t>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>LAGGING_SELF</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -1451,18 +1534,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T6" s="15" t="inlineStr">
+      <c r="T6" s="17" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>Rule: 3 ayri pattern (ilk kez, pes pese, frequency) + lagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
+          <t>Musterinin kendi faktoring kullanimi; olay zaten gerceklesmis (self-lagging).</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>3 ayri pattern kurali model degiskeni yerine rule katmaninda deger uretir; base feature olarak Faz 1'e alinmadi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
@@ -1479,7 +1567,7 @@
           <t>bank_debt_to_ebitda</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>FAZ1</t>
         </is>
@@ -1554,18 +1642,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T7" s="13" t="inlineStr">
+      <c r="T7" s="15" t="inlineStr">
         <is>
           <t>DAHIL</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>TLREF normalize edilmis kaldirac; ham oran modele girer, 1-esigi rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
+          <t>Leading: TLREF-normalize edilmis musteri kendi kaldiraci.</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>Ham oran modele base olarak girer; '1 uzeri kosulu' rule layer'a birakildi. Bilanco cohort'una dogrudan uygulanabiliyor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1">
       <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
@@ -1582,7 +1675,7 @@
           <t>trade_receivables_to_turnover</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>FAZ1</t>
         </is>
@@ -1657,18 +1750,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T8" s="13" t="inlineStr">
+      <c r="T8" s="15" t="inlineStr">
         <is>
           <t>DAHIL</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>Isletme sermayesi sinyali; bilanco bazli leading</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>Leading: musterinin kendi bilanco isletme sermayesi orani.</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>Bilanco cohort'una uygulanabilen temel isletme saglik metrigi; sure-tahsilat baskisini yakalar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
@@ -1685,7 +1783,7 @@
           <t>profitability_to_turnover</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>FAZ1</t>
         </is>
@@ -1760,18 +1858,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T9" s="13" t="inlineStr">
+      <c r="T9" s="15" t="inlineStr">
         <is>
           <t>DAHIL</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>Operasyonel saglik margin'i</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
+          <t>Leading: musterinin kendi operasyonel karlilik margini.</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>Bilanco cohort'una uygulanabiliyor; margin erosion'u olcmek icin sade ve yorumlanabilir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1">
       <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
@@ -1788,9 +1891,9 @@
           <t>electricity_bill_amount_change</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>SEGMENT</t>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>SEGMENT_SPECIFIC</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1863,18 +1966,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T10" s="15" t="inlineStr">
+      <c r="T10" s="17" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>Segment-specific: sadece NACE C (imalat) icin</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
+          <t>Yalniz NACE section C (imalat) icin tanimli; genel kohorta uygulanamaz.</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>Faz 1 kapsayici skora giremez; ileri fazda imalat alt modelinin feature'i olur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
@@ -1891,9 +1999,9 @@
           <t>business_loan_vs_inflation</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>BIDIRECTIONAL_OR_JUDGMENT</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1966,18 +2074,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T11" s="15" t="inlineStr">
+      <c r="T11" s="17" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>Judgment-heavy: 'duzenli/dengeli artis kotu degil' ifadesi rule karakteri</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
+          <t>Yargi gerektiriyor: 'enflasyon uyumlu buyume kotu degil' ifadesi deterministic bir oran/esik halinde olculmuyor.</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>Standardize edilemedigi icin Faz 1 genel kapsayici skora alinmadi; business team ek kural tanimlamali.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1">
       <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
@@ -1994,7 +2107,7 @@
           <t>equity_change</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>FAZ1</t>
         </is>
@@ -2069,18 +2182,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T12" s="13" t="inlineStr">
+      <c r="T12" s="15" t="inlineStr">
         <is>
           <t>DAHIL</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>Sermaye saglamligi; negatif flag rule olarak companion</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
+          <t>Leading: musterinin kendi sermaye saglamligi degisimi.</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>Bilanco cohort'unda anlamli; negatif ozkaynak flag rule katmaninda companion olarak calisir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1">
       <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
@@ -2097,9 +2215,9 @@
           <t>delinquency_entry_or_frequency</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>RULE</t>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>LAGGING_SELF</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -2172,18 +2290,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T13" s="15" t="inlineStr">
+      <c r="T13" s="17" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>Pure rule: 3 pattern + lagging (gecikme zaten olmus)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
+          <t>Musterinin kendi gecikme olayi zaten gerceklesmis; event-count lagging.</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>Erken uyari skoru degil, gerceklesmis olumsuzluk sinyali; companion rule'lara birakildi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1">
       <c r="A14" s="3" t="n">
         <v>13</v>
       </c>
@@ -2200,9 +2323,9 @@
           <t>credit_card_full_payment_break</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
-        <is>
-          <t>RULE</t>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>LAGGING_SELF</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -2275,18 +2398,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T14" s="15" t="inlineStr">
+      <c r="T14" s="17" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>Pure rule: 'son 2 yilda ilk kez', '2 ay pes pese' + lagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
+          <t>Musterinin kendi odememe olayi gerceklesmis; self-lagging.</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>Olay sonrasi sinyal; Faz 1 kapsayici erken uyari skorunun disinda, rule katmaninda kullanilacak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="80" customHeight="1">
       <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
@@ -2303,7 +2431,7 @@
           <t>ifrs9_behavioral_pd</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>FAZ1</t>
         </is>
@@ -2378,18 +2506,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T15" s="13" t="inlineStr">
+      <c r="T15" s="15" t="inlineStr">
         <is>
           <t>DAHIL</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>Authoritative risk proxy; %2 alti rule olarak companion</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
+          <t>Leading: authoritative davranis bazli temerrut olasiligi; musterinin kendi risk proxy'si.</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>Ham PD modele girer; '%2 alti disla' esik rule katmaninda companion. Tum Ticari Orta'ya uygulanabilir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1">
       <c r="A16" s="3" t="n">
         <v>15</v>
       </c>
@@ -2406,7 +2539,7 @@
           <t>kkb_commercial_score</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>FAZ1</t>
         </is>
@@ -2481,18 +2614,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T16" s="13" t="inlineStr">
+      <c r="T16" s="15" t="inlineStr">
         <is>
           <t>DAHIL</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>Authoritative external credit score</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1">
+          <t>Leading: authoritative dis kredi notu; musterinin kendi kredi profili.</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>Genel kohorta uygulanabilir; peer karsilastirmasi yapmadan authoritative kaynak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="80" customHeight="1">
       <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
@@ -2509,7 +2647,7 @@
           <t>kkb_indebtedness_index</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>FAZ1</t>
         </is>
@@ -2584,18 +2722,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T17" s="13" t="inlineStr">
+      <c r="T17" s="15" t="inlineStr">
         <is>
           <t>DAHIL</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>Authoritative external indebtedness index</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="60" customHeight="1">
+          <t>Leading: authoritative dis borcluluk endeksi; musterinin kendi kaldirac profili.</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>Genel kohorta uygulanabilir; KKB verisinin diger base'lere gore bagimsiz sinyali.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="80" customHeight="1">
       <c r="A18" s="3" t="n">
         <v>17</v>
       </c>
@@ -2612,7 +2755,7 @@
           <t>net_sales_change</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>FAZ1</t>
         </is>
@@ -2687,18 +2830,23 @@
           <t>yes (population_percentile, median_ratio)</t>
         </is>
       </c>
-      <c r="T18" s="13" t="inlineStr">
+      <c r="T18" s="15" t="inlineStr">
         <is>
           <t>DAHIL</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>Ciro buyume hizi; population reference ile peer karsilastirma</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="60" customHeight="1">
+          <t>Leading: musterinin kendi ciro buyumesi YoY.</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>Bilanco cohort'unda uygulanabilir; population reference peer karsilastirmasi sektorel etkileri hafifletir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="80" customHeight="1">
       <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
@@ -2715,9 +2863,9 @@
           <t>memzuc_limit_change</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>BIDIRECTIONAL_OR_JUDGMENT</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -2790,18 +2938,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T19" s="15" t="inlineStr">
+      <c r="T19" s="17" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t>Bidirectional: azalma iyi veya kotu olabilir, dar sinyal</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="60" customHeight="1">
+          <t>Bidirectional: limit azalisi iyi (risk dustu) veya kotu (banka limiti kisiyor) anlamina gelebilir; deterministic yon yok.</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>Standardize yon olmadan Faz 1 kapsayici skoruna katkisiz; rule/insight olarak ayri kullanilabilir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="80" customHeight="1">
       <c r="A20" s="3" t="n">
         <v>19</v>
       </c>
@@ -2818,9 +2971,9 @@
           <t>memzuc_bank_count_change</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>BIDIRECTIONAL_OR_JUDGMENT</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -2893,18 +3046,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T20" s="15" t="inlineStr">
+      <c r="T20" s="17" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>Bidirectional + dar sinyal katkisi</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
+          <t>Bidirectional: banka sayisi azalmasi kredibilite dusuklugu de olabilir, borc toplanmasi da olabilir.</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>Yon belirsizligi nedeniyle kapsayici skora katkisi guvenli degil; Faz 1 disinda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="80" customHeight="1">
       <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
@@ -2921,7 +3079,7 @@
           <t>electricity_payment_failure</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>RULE</t>
         </is>
@@ -2996,18 +3154,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T21" s="15" t="inlineStr">
+      <c r="T21" s="17" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t>Rule + segment-specific + lagging: 3 sebep birden</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="60" customHeight="1">
+          <t>Tam pattern kurali: 'son 2 yilda ilk kez gec odeme', 'son 1 yilda 2 kez pes pese'. Modele girecek surekli bir metrik yok. Ek kisitlayici: elektrik abonesi alt evreni.</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>Rule katmanina birakildi; Faz 1 kapsayici genel skorun disinda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="80" customHeight="1">
       <c r="A22" s="3" t="n">
         <v>21</v>
       </c>
@@ -3024,9 +3187,9 @@
           <t>kkb_check_portfolio_quality_deterioration</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>NARROW_SCOPE</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -3099,18 +3262,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T22" s="15" t="inlineStr">
+      <c r="T22" s="17" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>Dar coverage + ambiguous; genel skora katki dusuk</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="60" customHeight="1">
+          <t>Metodoloji leading ama kapsam dar: sadece KKB cek raporu coverage'i olan musteriler.</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>Genel kohort'un onemli bir parcasina uygulanamaz; Faz 1 kapsayici skorunda disarida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="80" customHeight="1">
       <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
@@ -3127,7 +3295,7 @@
           <t>memzuc_limit_utilization_increase</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>FAZ1</t>
         </is>
@@ -3202,18 +3370,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T23" s="13" t="inlineStr">
+      <c r="T23" s="15" t="inlineStr">
         <is>
           <t>DAHIL</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>Kaldirac tepki davranisi; Ticari Orta kapsamindaki kisim alindi</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="60" customHeight="1">
+          <t>Leading: musterinin kendi kullanim/stres sinyali; oran deterministic.</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>Ticari Orta (Tarim haric) Faz 1 kohortunda uygulanabilir; model bu metrigin nokta degerini ve delta/z turevlerini ayirt edebiliyor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="80" customHeight="1">
       <c r="A24" s="3" t="n">
         <v>23</v>
       </c>
@@ -3230,9 +3403,9 @@
           <t>livestock_count_change</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>SEGMENT</t>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>SEGMENT_SPECIFIC</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -3305,18 +3478,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T24" s="15" t="inlineStr">
+      <c r="T24" s="17" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t>Pure segment-specific: sadece Tarim-Hayvancilik</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="60" customHeight="1">
+          <t>Yalniz Tarim-Hayvancilik alt segmenti; Faz 1 ana kohortunda applicability yok.</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>Ileri fazda Tarim alt modelinde kullanilir; Faz 1'de kapsam disi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="80" customHeight="1">
       <c r="A25" s="3" t="n">
         <v>24</v>
       </c>
@@ -3333,9 +3511,9 @@
           <t>issuer_adverse_to_receivables</t>
         </is>
       </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>LAGGING</t>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>COUNTERPARTY</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -3408,18 +3586,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T25" s="15" t="inlineStr">
+      <c r="T25" s="17" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t>Lagging: kesideci olumsuzluk zaten yasanmis</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="60" customHeight="1">
+          <t>Musterinin kendi olumsuzlugu degil: musterinin elindeki cekin kesidecisi (counterparty) olumsuzluk yasamis.</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>Counterparty risk sinyali; Faz 1 kapsayici 'musteri kendi leading' ilkesinin disinda. Gelecekte counterparty alt modulune gider.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="80" customHeight="1">
       <c r="A26" s="3" t="n">
         <v>25</v>
       </c>
@@ -3436,9 +3619,9 @@
           <t>suspicious_receivables_to_receivables</t>
         </is>
       </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>LAGGING</t>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>COUNTERPARTY</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -3511,18 +3694,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T26" s="15" t="inlineStr">
+      <c r="T26" s="17" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>Lagging: alacak zaten 128-228'e supheli olarak ayrilmis</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="60" customHeight="1">
+          <t>Musterinin kendi alacagi supheli; yani alici (counterparty) odeyemedigi icin bilancoda ayrilmis. Musterinin bizzat leading sinyali degil.</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>Faz 1'de disarida; counterparty risk bilesenini ileri faz alt modulune erteledik.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="80" customHeight="1">
       <c r="A27" s="3" t="n">
         <v>26</v>
       </c>
@@ -3539,9 +3727,9 @@
           <t>forward_check_to_notes_payable_ratio</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>RULE</t>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>LAGGING_SELF</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -3614,18 +3802,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T27" s="15" t="inlineStr">
+      <c r="T27" s="17" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t>Esikli rule: '1 uzeri koşuluyla' ifadesi dogrudan threshold kurali</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="60" customHeight="1">
+          <t>Musterinin kendi ileri vadeli cek bindirmesi; '1 uzeri kosulu' esik kurali ile lagging bolgesine giriyor.</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>Ham oran model degiskeni degil esik sonrasi rule olarak calisir; base feature olarak Faz 1'de tutulmadi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="80" customHeight="1">
       <c r="A28" s="3" t="n">
         <v>27</v>
       </c>
@@ -3642,9 +3835,9 @@
           <t>returned_check_note_ratio</t>
         </is>
       </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>LAGGING</t>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>COUNTERPARTY</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -3717,18 +3910,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T28" s="15" t="inlineStr">
+      <c r="T28" s="17" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t>Lagging: iade zaten yasanmis</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="60" customHeight="1">
+          <t>Musterinin bankamiza tahsil icin verdigi cekler/senetler iade olmus; kesideci (counterparty) odeyememis. Musterinin kendi olayi degil.</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>Counterparty risk; Faz 1 kapsayici 'musteri kendi leading' skoruna katki tutumlu. Ileri fazda ayri modul.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="80" customHeight="1">
       <c r="A29" s="3" t="n">
         <v>28</v>
       </c>
@@ -3745,9 +3943,9 @@
           <t>bank_asset_average_change</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>NARROW_SCOPE</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -3820,18 +4018,23 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T29" s="15" t="inlineStr">
+      <c r="T29" s="17" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t>Dar kapsam (sadece bankamizdaki varlik) + ambiguous</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="60" customHeight="1">
+          <t>Metodoloji leading (varlik azalmasi risk sinyali) ama olculen sadece bankamizdaki varlik; musterinin toplam varligi gorulemiyor (dar kapsam).</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>Faz 1'de tam kapsamda anlamli sinyal uretemiyor; multi-bank tablosu olmadan bu metrik peer'lerle karsilastirilamaz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="80" customHeight="1">
       <c r="A30" s="3" t="n">
         <v>29</v>
       </c>
@@ -3848,9 +4051,9 @@
           <t>insurance_claim_to_receivables</t>
         </is>
       </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>LAGGING</t>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>COUNTERPARTY</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -3923,19 +4126,24 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T30" s="15" t="inlineStr">
+      <c r="T30" s="17" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>Lagging (hasar odenmis) + %15 filter rule</t>
+          <t>Musterinin kendi olumsuzlugu degil: musterinin alicisi odeyemedigi icin sigorta sirketi tazmin yapmis. Counterparty risk sinyali.</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>Ek olarak %15 alti filter rule; Faz 1 kapsayici 'musteri kendi leading' ilkesine uymuyor, ileri faz counterparty modulune kaldirildi.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U30"/>
+  <autoFilter ref="A1:V30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3960,42 +4168,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Canonical Name</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Formula</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Business Heading</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Yilliklastirma</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Missing Semantics</t>
         </is>
@@ -4005,7 +4213,7 @@
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="19" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>bank_debt_to_turnover</t>
         </is>
@@ -4045,7 +4253,7 @@
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>pos_volume_change</t>
         </is>
@@ -4085,7 +4293,7 @@
       <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>bank_debt_to_ebitda</t>
         </is>
@@ -4125,7 +4333,7 @@
       <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>trade_receivables_to_turnover</t>
         </is>
@@ -4165,7 +4373,7 @@
       <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>profitability_to_turnover</t>
         </is>
@@ -4205,7 +4413,7 @@
       <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>equity_change</t>
         </is>
@@ -4245,7 +4453,7 @@
       <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>ifrs9_behavioral_pd</t>
         </is>
@@ -4285,7 +4493,7 @@
       <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>kkb_commercial_score</t>
         </is>
@@ -4325,7 +4533,7 @@
       <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>kkb_indebtedness_index</t>
         </is>
@@ -4365,7 +4573,7 @@
       <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>net_sales_change</t>
         </is>
@@ -4405,7 +4613,7 @@
       <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>memzuc_limit_utilization_increase</t>
         </is>
@@ -4453,7 +4661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4464,27 +4672,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Final Column</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Column Type</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Hesaplama / Donusum</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Kaynak Business Heading</t>
         </is>
@@ -4494,12 +4702,12 @@
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="19" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>customer_id</t>
         </is>
       </c>
-      <c r="C2" s="20" t="inlineStr">
+      <c r="C2" s="24" t="inlineStr">
         <is>
           <t>technical_pass_through</t>
         </is>
@@ -4519,12 +4727,12 @@
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>snapshot_date</t>
         </is>
       </c>
-      <c r="C3" s="20" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>technical_pass_through</t>
         </is>
@@ -4544,12 +4752,12 @@
       <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>segment</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>technical_pass_through</t>
         </is>
@@ -4569,12 +4777,12 @@
       <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>bank_debt_to_turnover</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>derived_base</t>
         </is>
@@ -4594,12 +4802,12 @@
       <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>pos_volume_change</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>derived_base</t>
         </is>
@@ -4619,12 +4827,12 @@
       <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>bank_debt_to_ebitda</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>derived_base</t>
         </is>
@@ -4644,12 +4852,12 @@
       <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>trade_receivables_to_turnover</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>derived_base</t>
         </is>
@@ -4669,12 +4877,12 @@
       <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>profitability_to_turnover</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>derived_base</t>
         </is>
@@ -4694,12 +4902,12 @@
       <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>equity_change</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t>derived_base</t>
         </is>
@@ -4719,12 +4927,12 @@
       <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>ifrs9_behavioral_pd</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>passthrough_base</t>
         </is>
@@ -4744,12 +4952,12 @@
       <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>kkb_commercial_score</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t>passthrough_base</t>
         </is>
@@ -4769,12 +4977,12 @@
       <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>kkb_indebtedness_index</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>passthrough_base</t>
         </is>
@@ -4794,12 +5002,12 @@
       <c r="A14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>net_sales_change</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>derived_base</t>
         </is>
@@ -4819,12 +5027,12 @@
       <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>memzuc_limit_utilization_increase</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>derived_base</t>
         </is>
@@ -4844,12 +5052,12 @@
       <c r="A16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>bank_debt_to_turnover__delta_1</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -4869,12 +5077,12 @@
       <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>bank_debt_to_turnover__self_zscore_6</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -4894,12 +5102,12 @@
       <c r="A18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>pos_volume_change__delta_1</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -4919,12 +5127,12 @@
       <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>pos_volume_change__self_zscore_6</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="26" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -4944,12 +5152,12 @@
       <c r="A20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>bank_debt_to_ebitda__delta_1</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -4969,12 +5177,12 @@
       <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>bank_debt_to_ebitda__self_zscore_6</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="26" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -4994,12 +5202,12 @@
       <c r="A22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>trade_receivables_to_turnover__delta_1</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="26" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5019,12 +5227,12 @@
       <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="19" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>trade_receivables_to_turnover__self_zscore_6</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="26" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5044,12 +5252,12 @@
       <c r="A24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>profitability_to_turnover__delta_1</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="26" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5069,12 +5277,12 @@
       <c r="A25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>profitability_to_turnover__self_zscore_6</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="26" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5094,12 +5302,12 @@
       <c r="A26" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>equity_change__delta_1</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5119,12 +5327,12 @@
       <c r="A27" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="19" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>equity_change__self_zscore_6</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="26" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5144,12 +5352,12 @@
       <c r="A28" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="19" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>ifrs9_behavioral_pd__delta_1</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5169,12 +5377,12 @@
       <c r="A29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="19" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>ifrs9_behavioral_pd__self_zscore_6</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5194,12 +5402,12 @@
       <c r="A30" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="19" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>kkb_commercial_score__delta_1</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="26" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5219,12 +5427,12 @@
       <c r="A31" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="19" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>kkb_commercial_score__self_zscore_6</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="26" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5244,12 +5452,12 @@
       <c r="A32" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="19" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>kkb_indebtedness_index__delta_1</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="26" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5269,12 +5477,12 @@
       <c r="A33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="19" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>kkb_indebtedness_index__self_zscore_6</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5294,12 +5502,12 @@
       <c r="A34" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="19" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>net_sales_change__delta_1</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C34" s="26" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5319,12 +5527,12 @@
       <c r="A35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="19" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>net_sales_change__self_zscore_6</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C35" s="26" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5344,12 +5552,12 @@
       <c r="A36" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="19" t="inlineStr">
+      <c r="B36" s="23" t="inlineStr">
         <is>
           <t>memzuc_limit_utilization_increase__delta_1</t>
         </is>
       </c>
-      <c r="C36" s="22" t="inlineStr">
+      <c r="C36" s="26" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5369,12 +5577,12 @@
       <c r="A37" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="19" t="inlineStr">
+      <c r="B37" s="23" t="inlineStr">
         <is>
           <t>memzuc_limit_utilization_increase__self_zscore_6</t>
         </is>
       </c>
-      <c r="C37" s="22" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5394,12 +5602,12 @@
       <c r="A38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="19" t="inlineStr">
+      <c r="B38" s="23" t="inlineStr">
         <is>
           <t>pos_volume_change__trend_slope_6</t>
         </is>
       </c>
-      <c r="C38" s="23" t="inlineStr">
+      <c r="C38" s="27" t="inlineStr">
         <is>
           <t>trend</t>
         </is>
@@ -5419,12 +5627,12 @@
       <c r="A39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="19" t="inlineStr">
+      <c r="B39" s="23" t="inlineStr">
         <is>
           <t>net_sales_change__trend_slope_6</t>
         </is>
       </c>
-      <c r="C39" s="23" t="inlineStr">
+      <c r="C39" s="27" t="inlineStr">
         <is>
           <t>trend</t>
         </is>
@@ -5444,12 +5652,12 @@
       <c r="A40" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="19" t="inlineStr">
+      <c r="B40" s="23" t="inlineStr">
         <is>
           <t>pos_volume_change__population_percentile</t>
         </is>
       </c>
-      <c r="C40" s="24" t="inlineStr">
+      <c r="C40" s="28" t="inlineStr">
         <is>
           <t>population_reference</t>
         </is>
@@ -5469,12 +5677,12 @@
       <c r="A41" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="19" t="inlineStr">
+      <c r="B41" s="23" t="inlineStr">
         <is>
           <t>pos_volume_change__vs_population_median_delta</t>
         </is>
       </c>
-      <c r="C41" s="24" t="inlineStr">
+      <c r="C41" s="28" t="inlineStr">
         <is>
           <t>population_reference</t>
         </is>
@@ -5494,12 +5702,12 @@
       <c r="A42" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="19" t="inlineStr">
+      <c r="B42" s="23" t="inlineStr">
         <is>
           <t>net_sales_change__population_percentile</t>
         </is>
       </c>
-      <c r="C42" s="24" t="inlineStr">
+      <c r="C42" s="28" t="inlineStr">
         <is>
           <t>population_reference</t>
         </is>
@@ -5519,12 +5727,12 @@
       <c r="A43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="19" t="inlineStr">
+      <c r="B43" s="23" t="inlineStr">
         <is>
           <t>net_sales_change__vs_population_median_delta</t>
         </is>
       </c>
-      <c r="C43" s="24" t="inlineStr">
+      <c r="C43" s="28" t="inlineStr">
         <is>
           <t>population_reference</t>
         </is>
@@ -5538,83 +5746,6 @@
         <is>
           <t>Net Satis (Ciro)</t>
         </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Ozet</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="25" t="inlineStr">
-        <is>
-          <t>Teknik pass-through</t>
-        </is>
-      </c>
-      <c r="C46" s="25" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="25" t="inlineStr">
-        <is>
-          <t>Derived base (ratio/yoy)</t>
-        </is>
-      </c>
-      <c r="C47" s="25" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="25" t="inlineStr">
-        <is>
-          <t>Passthrough base (PD + 2 KKB)</t>
-        </is>
-      </c>
-      <c r="C48" s="25" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="25" t="inlineStr">
-        <is>
-          <t>Self-history (delta_1 + self_zscore_6)</t>
-        </is>
-      </c>
-      <c r="C49" s="25" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="25" t="inlineStr">
-        <is>
-          <t>Trend slope (6m)</t>
-        </is>
-      </c>
-      <c r="C50" s="25" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="25" t="inlineStr">
-        <is>
-          <t>Population reference</t>
-        </is>
-      </c>
-      <c r="C51" s="25" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>TOPLAM</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -5640,27 +5771,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Native Column</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Aciklama</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Hangi Derived Feature'i Besler</t>
         </is>
@@ -5670,7 +5801,7 @@
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="19" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>customer_id</t>
         </is>
@@ -5695,7 +5826,7 @@
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>snapshot_date</t>
         </is>
@@ -5720,7 +5851,7 @@
       <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>segment</t>
         </is>
@@ -5745,7 +5876,7 @@
       <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>is_balance_sheet_customer</t>
         </is>
@@ -5770,7 +5901,7 @@
       <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>has_pos</t>
         </is>
@@ -5795,7 +5926,7 @@
       <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>nace_section</t>
         </is>
@@ -5820,7 +5951,7 @@
       <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>nace_main</t>
         </is>
@@ -5845,7 +5976,7 @@
       <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>fs_period_code</t>
         </is>
@@ -5870,7 +6001,7 @@
       <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>fs_last_update_date</t>
         </is>
@@ -5895,7 +6026,7 @@
       <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>memzuc_total_cash_risk_0_24m</t>
         </is>
@@ -5920,7 +6051,7 @@
       <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>tlref_factor</t>
         </is>
@@ -5945,7 +6076,7 @@
       <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>fs_net_sales_cumulative</t>
         </is>
@@ -5970,7 +6101,7 @@
       <c r="A14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>fs_ebitda_cumulative</t>
         </is>
@@ -5995,7 +6126,7 @@
       <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>fs_trade_receivables</t>
         </is>
@@ -6020,7 +6151,7 @@
       <c r="A16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>fs_notes_receivable</t>
         </is>
@@ -6045,7 +6176,7 @@
       <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>fs_net_profit_cumulative</t>
         </is>
@@ -6070,7 +6201,7 @@
       <c r="A18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>fs_equity</t>
         </is>
@@ -6095,7 +6226,7 @@
       <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>pos_monthly_volume</t>
         </is>
@@ -6120,7 +6251,7 @@
       <c r="A20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>ifrs9_behavioral_pd</t>
         </is>
@@ -6145,7 +6276,7 @@
       <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>kkb_commercial_score</t>
         </is>
@@ -6170,7 +6301,7 @@
       <c r="A22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>kkb_indebtedness_index</t>
         </is>
@@ -6195,7 +6326,7 @@
       <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="19" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>memzuc_total_limit</t>
         </is>
@@ -6220,7 +6351,7 @@
       <c r="A24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>memzuc_total_risk</t>
         </is>
@@ -6253,435 +6384,531 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="75" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Canonical Name</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Business Basligi</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
-        <is>
-          <t>Dislama Gerekcesi</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>Kategori Gerekcesi</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Secim Gerekcesi (Faz 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>LAGGING_SELF</t>
+        </is>
+      </c>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>seizure_amount_to_turnover</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Haciz Tutari ve Ciro Iliskisi</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Musterinin kendi olumsuzlugu: devam eden haciz zaten yasanmis bir olay (self-lagging). Rule pattern'i 'ilk kez 24m' sadece companion filtredir.</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Kapsayici erken uyari skoruna katkisi sinirli; olay gerceklestikten sonra sinyal uretir. Faz 2'de rule katmaninda kullanilacak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>LAGGING_SELF</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>factoring_risk_presence</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Faktoring</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Musterinin kendi faktoring kullanimi; olay zaten gerceklesmis (self-lagging).</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>3 ayri pattern kurali model degiskeni yerine rule katmaninda deger uretir; base feature olarak Faz 1'e alinmadi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>LAGGING_SELF</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>delinquency_entry_or_frequency</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Musterinin Bankamizda veya Diger Bankalarda Gecikmeye Girme</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Musterinin kendi gecikme olayi zaten gerceklesmis; event-count lagging.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Erken uyari skoru degil, gerceklesmis olumsuzluk sinyali; companion rule'lara birakildi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>LAGGING_SELF</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>credit_card_full_payment_break</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Musterinin Bankamizdaki Kredi Karti Borcunun Tamamini Odememesi</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Musterinin kendi odememe olayi gerceklesmis; self-lagging.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Olay sonrasi sinyal; Faz 1 kapsayici erken uyari skorunun disinda, rule katmaninda kullanilacak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>LAGGING_SELF</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>forward_check_to_notes_payable_ratio</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>KKB Ileri Vadeli Cek ve Bilanco Senetli Borc / Verilen Cek Iliskisi</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Musterinin kendi ileri vadeli cek bindirmesi; '1 uzeri kosulu' esik kurali ile lagging bolgesine giriyor.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Ham oran model degiskeni degil esik sonrasi rule olarak calisir; base feature olarak Faz 1'de tutulmadi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>COUNTERPARTY</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>issuer_adverse_to_receivables</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Kesideci Olumsuzlugu ve Bilanco Ticari Alacak Iliskisi</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Musterinin kendi olumsuzlugu degil: musterinin elindeki cekin kesidecisi (counterparty) olumsuzluk yasamis.</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Counterparty risk sinyali; Faz 1 kapsayici 'musteri kendi leading' ilkesinin disinda. Gelecekte counterparty alt modulune gider.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>COUNTERPARTY</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>suspicious_receivables_to_receivables</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Supheli Ticari Alacaklar ve Ticari Alacak Iliskisi</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Musterinin kendi alacagi supheli; yani alici (counterparty) odeyemedigi icin bilancoda ayrilmis. Musterinin bizzat leading sinyali degil.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Faz 1'de disarida; counterparty risk bilesenini ileri faz alt modulune erteledik.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>COUNTERPARTY</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>returned_check_note_ratio</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Bankamizdaki Cek/Senet Iade Orani</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Musterinin bankamiza tahsil icin verdigi cekler/senetler iade olmus; kesideci (counterparty) odeyememis. Musterinin kendi olayi degil.</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Counterparty risk; Faz 1 kapsayici 'musteri kendi leading' skoruna katki tutumlu. Ileri fazda ayri modul.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>COUNTERPARTY</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>insurance_claim_to_receivables</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Alacak Sigortasi Tazmin Verisi ve Bilanco Ticari Alacak Iliskisi</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Musterinin kendi olumsuzlugu degil: musterinin alicisi odeyemedigi icin sigorta sirketi tazmin yapmis. Counterparty risk sinyali.</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Ek olarak %15 alti filter rule; Faz 1 kapsayici 'musteri kendi leading' ilkesine uymuyor, ileri faz counterparty modulune kaldirildi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>RULE</t>
         </is>
       </c>
-      <c r="B2" s="19" t="inlineStr">
-        <is>
-          <t>seizure_amount_to_turnover</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Haciz Tutari ve Ciro Iliskisi</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Rule: 'son 2 yilda ilk kez haciz' pattern + lagging (haciz zaten var)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>check_payment_time_shift</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Cek Odemesi Zamani</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Tam pattern kurgusu: 'son 6 ayda ilk kez ogleden sonra', 'son 3 ayda pes pese farkli gun'. Modele girecek surekli oran/indikator yok, sadece deterministic event pattern'leri.</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Modelleme degiskeni olamaz (tek sayisi/orani yok); rule katmaninda companion olarak calisir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>RULE</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
-        <is>
-          <t>check_payment_time_shift</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Cek Odemesi Zamani</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Rule: 'son 6 ayda ilk kez', 'son 3 ayda pes pese farkli gunler'</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>RULE</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>factoring_risk_presence</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Faktoring</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Rule: 3 ayri pattern (ilk kez, pes pese, frequency) + lagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>RULE</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>delinquency_entry_or_frequency</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Musterinin Bankamizda veya Diger Bankalarda Gecikmeye Girme</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Pure rule: 3 pattern + lagging (gecikme zaten olmus)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>RULE</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>credit_card_full_payment_break</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Musterinin Bankamizdaki Kredi Karti Borcunun Tamamini Odememesi</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Pure rule: 'son 2 yilda ilk kez', '2 ay pes pese' + lagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>RULE</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>electricity_payment_failure</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Elektrik Borcunu Odeyemeyenler</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Rule + segment-specific + lagging: 3 sebep birden</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>RULE</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>forward_check_to_notes_payable_ratio</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>KKB Ileri Vadeli Cek ve Bilanco Senetli Borc / Verilen Cek Iliskisi</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Esikli rule: '1 uzeri koşuluyla' ifadesi dogrudan threshold kurali</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>SEGMENT</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Tam pattern kurali: 'son 2 yilda ilk kez gec odeme', 'son 1 yilda 2 kez pes pese'. Modele girecek surekli bir metrik yok. Ek kisitlayici: elektrik abonesi alt evreni.</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Rule katmanina birakildi; Faz 1 kapsayici genel skorun disinda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>SEGMENT_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>electricity_bill_amount_change</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Musterinin Aylik Elektrik Fatura Tutarlari (NACE imalat)</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Segment-specific: sadece NACE C (imalat) icin</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>SEGMENT</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Yalniz NACE section C (imalat) icin tanimli; genel kohorta uygulanamaz.</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Faz 1 kapsayici skora giremez; ileri fazda imalat alt modelinin feature'i olur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>SEGMENT_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>livestock_count_change</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Hayvan Sayisi</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Pure segment-specific: sadece Tarim-Hayvancilik</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>LAGGING</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>issuer_adverse_to_receivables</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Kesideci Olumsuzlugu ve Bilanco Ticari Alacak Iliskisi</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Lagging: kesideci olumsuzluk zaten yasanmis</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>LAGGING</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>suspicious_receivables_to_receivables</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Supheli Ticari Alacaklar ve Ticari Alacak Iliskisi</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Lagging: alacak zaten 128-228'e supheli olarak ayrilmis</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>LAGGING</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>returned_check_note_ratio</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Bankamizdaki Cek/Senet Iade Orani</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Lagging: iade zaten yasanmis</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>LAGGING</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>insurance_claim_to_receivables</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Alacak Sigortasi Tazmin Verisi ve Bilanco Ticari Alacak Iliskisi</t>
-        </is>
-      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Lagging (hasar odenmis) + %15 filter rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
+          <t>Yalniz Tarim-Hayvancilik alt segmenti; Faz 1 ana kohortunda applicability yok.</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Ileri fazda Tarim alt modelinde kullanilir; Faz 1'de kapsam disi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>NARROW_SCOPE</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>kkb_check_portfolio_quality_deterioration</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>KKB Cek Portfoy Kalitesinde Bozulma</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Metodoloji leading ama kapsam dar: sadece KKB cek raporu coverage'i olan musteriler.</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Genel kohort'un onemli bir parcasina uygulanamaz; Faz 1 kapsayici skorunda disarida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>NARROW_SCOPE</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>bank_asset_average_change</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Bankamizda Bulunan Mevduat / Varlik Ortalamalari</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Metodoloji leading (varlik azalmasi risk sinyali) ama olculen sadece bankamizdaki varlik; musterinin toplam varligi gorulemiyor (dar kapsam).</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Faz 1'de tam kapsamda anlamli sinyal uretemiyor; multi-bank tablosu olmadan bu metrik peer'lerle karsilastirilamaz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>BIDIRECTIONAL_OR_JUDGMENT</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>business_loan_vs_inflation</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Musterinin Bankalardaki Isletme Borclari ve Enflasyon Iliskisi</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Judgment-heavy: 'duzenli/dengeli artis kotu degil' ifadesi rule karakteri</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Yargi gerektiriyor: 'enflasyon uyumlu buyume kotu degil' ifadesi deterministic bir oran/esik halinde olculmuyor.</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Standardize edilemedigi icin Faz 1 genel kapsayici skora alinmadi; business team ek kural tanimlamali.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>BIDIRECTIONAL_OR_JUDGMENT</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>memzuc_limit_change</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Memzuc Limit Azalisi</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Bidirectional: azalma iyi veya kotu olabilir, dar sinyal</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Bidirectional: limit azalisi iyi (risk dustu) veya kotu (banka limiti kisiyor) anlamina gelebilir; deterministic yon yok.</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Standardize yon olmadan Faz 1 kapsayici skoruna katkisiz; rule/insight olarak ayri kullanilabilir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>BIDIRECTIONAL_OR_JUDGMENT</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>memzuc_bank_count_change</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Memzuc Banka Sayisi Azalisi</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Bidirectional + dar sinyal katkisi</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>kkb_check_portfolio_quality_deterioration</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>KKB Cek Portfoy Kalitesinde Bozulma</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Dar coverage + ambiguous; genel skora katki dusuk</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>bank_asset_average_change</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Bankamizda Bulunan Mevduat / Varlik Ortalamalari</t>
-        </is>
-      </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Dar kapsam (sadece bankamizdaki varlik) + ambiguous</t>
+          <t>Bidirectional: banka sayisi azalmasi kredibilite dusuklugu de olabilir, borc toplanmasi da olabilir.</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Yon belirsizligi nedeniyle kapsayici skora katkisi guvenli degil; Faz 1 disinda.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D19"/>
+  <autoFilter ref="A1:E19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/dictionary/faz1_variable_dictionary.xlsx
+++ b/dictionary/faz1_variable_dictionary.xlsx
@@ -74,7 +74,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -113,11 +113,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
@@ -149,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -180,10 +175,7 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -204,9 +196,6 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -225,10 +214,10 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -649,12 +638,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Faz 1'e alinan base sayisi</t>
+          <t>Faz 1 secimi (DAHIL)</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>11 (hepsi LEADING kategorisinden)</t>
         </is>
       </c>
     </row>
@@ -709,144 +698,144 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Eleme kategorileri</t>
+          <t>Kategori seti</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>LAGGING_SELF, COUNTERPARTY, RULE, SEGMENT_SPECIFIC, NARROW_SCOPE, BIDIRECTIONAL_OR_JUDGMENT</t>
+          <t>LEADING, LAGGING_SELF, COUNTERPARTY, RULE, SEGMENT_SPECIFIC, BIDIRECTIONAL_OR_JUDGMENT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Oracle native tablo</t>
+          <t>Not</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>EWS_TO_FAZ1_NATIVE (23 kolon)</t>
+          <t>Kategori = degiskenin dogasi. Faz 1 Karari (DAHIL/DISI) ayri bir secimdir: bir degisken LEADING olup Faz 1 disinda kalabilir.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Oracle input tablo</t>
+          <t>Oracle native tablo</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>EWS_TO_FAZ1_INPUT (42 kolon)</t>
+          <t>EWS_TO_FAZ1_NATIVE (23 kolon)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Monitor history tablo</t>
+          <t>Oracle input tablo</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>EWS_TO_FAZ1_MONITOR_HISTORY (run bazli health metrikleri)</t>
+          <t>EWS_TO_FAZ1_INPUT (42 kolon)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Output tablo</t>
+          <t>Monitor history tablo</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
+          <t>EWS_TO_FAZ1_MONITOR_HISTORY (run bazli health metrikleri)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Output tablolar</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
           <t>EWS_TO_FAZ1_RESULTS / DETAILS / FEATURE_EFFECTS</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Renk Kodlari</t>
-        </is>
-      </c>
-    </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>FAZ1</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Faz 1 base setine alindi (11 degisken)</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Kategori Renk Kodlari</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>LEADING</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Musterinin kendi leading finansal/kredi sinyali (Faz 1 adayi). 12 degisken; 11'i Faz 1'e alindi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>LAGGING_SELF</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Musterinin kendi olumsuzluk olayi zaten gerceklesmis (haciz, gecikme, kredi karti, faktoring, forward check)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Musterinin kendi olumsuzluk olayi zaten gerceklesmis (haciz, gecikme, kredi karti, faktoring, forward check esik sonrasi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>COUNTERPARTY</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Musterinin kendi degil, karsi tarafinin (kesideci / alici / sigortali) olumsuzlugu</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>RULE</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Tam pattern kurgusu; surekli oran/indikator yok, sadece deterministic event pattern'leri (ilk kez, pes pese, frekans)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Tam pattern kurgusu; surekli oran/indikator yok, sadece deterministic event pattern'leri</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>SEGMENT_SPECIFIC</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Yalniz belirli NACE / alt portfoy icin tanimli</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>NARROW_SCOPE</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>Metodoloji leading ama kapsam dar (sadece bankamiz, belli urun)</t>
-        </is>
-      </c>
-    </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>BIDIRECTIONAL_OR_JUDGMENT</t>
         </is>
@@ -878,7 +867,7 @@
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="48" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
@@ -899,112 +888,112 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Sayfa</t>
         </is>
       </c>
-      <c r="C1" s="13" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>Business Basligi</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>Canonical Name</t>
         </is>
       </c>
-      <c r="E1" s="13" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="F1" s="13" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="G1" s="13" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>Portfolio Scope</t>
         </is>
       </c>
-      <c r="H1" s="13" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>Model Placement</t>
         </is>
       </c>
-      <c r="I1" s="13" t="inlineStr">
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>Source / Accounts</t>
         </is>
       </c>
-      <c r="J1" s="13" t="inlineStr">
+      <c r="J1" s="12" t="inlineStr">
         <is>
           <t>Period / Annualization</t>
         </is>
       </c>
-      <c r="K1" s="13" t="inlineStr">
+      <c r="K1" s="12" t="inlineStr">
         <is>
           <t>Calculation Logic</t>
         </is>
       </c>
-      <c r="L1" s="13" t="inlineStr">
+      <c r="L1" s="12" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="M1" s="13" t="inlineStr">
+      <c r="M1" s="12" t="inlineStr">
         <is>
           <t>Refresh Frequency</t>
         </is>
       </c>
-      <c r="N1" s="13" t="inlineStr">
+      <c r="N1" s="12" t="inlineStr">
         <is>
           <t>Freshness Rule</t>
         </is>
       </c>
-      <c r="O1" s="13" t="inlineStr">
+      <c r="O1" s="12" t="inlineStr">
         <is>
           <t>Applicable Segments</t>
         </is>
       </c>
-      <c r="P1" s="13" t="inlineStr">
+      <c r="P1" s="12" t="inlineStr">
         <is>
           <t>Model Treatment</t>
         </is>
       </c>
-      <c r="Q1" s="13" t="inlineStr">
+      <c r="Q1" s="12" t="inlineStr">
         <is>
           <t>Companion Rules / Filters</t>
         </is>
       </c>
-      <c r="R1" s="13" t="inlineStr">
+      <c r="R1" s="12" t="inlineStr">
         <is>
           <t>Recommended History Features</t>
         </is>
       </c>
-      <c r="S1" s="13" t="inlineStr">
+      <c r="S1" s="12" t="inlineStr">
         <is>
           <t>Population Reference</t>
         </is>
       </c>
-      <c r="T1" s="13" t="inlineStr">
+      <c r="T1" s="12" t="inlineStr">
         <is>
           <t>Faz 1 Karari</t>
         </is>
       </c>
-      <c r="U1" s="13" t="inlineStr">
+      <c r="U1" s="12" t="inlineStr">
         <is>
           <t>Kategori Gerekcesi</t>
         </is>
       </c>
-      <c r="V1" s="13" t="inlineStr">
+      <c r="V1" s="12" t="inlineStr">
         <is>
           <t>Secim Gerekcesi (Faz 1)</t>
         </is>
@@ -1027,9 +1016,9 @@
           <t>bank_debt_to_turnover</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
-        <is>
-          <t>FAZ1</t>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>LEADING</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -1102,7 +1091,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T2" s="15" t="inlineStr">
+      <c r="T2" s="14" t="inlineStr">
         <is>
           <t>DAHIL</t>
         </is>
@@ -1135,9 +1124,9 @@
           <t>pos_volume_change</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
-        <is>
-          <t>FAZ1</t>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>LEADING</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -1210,7 +1199,7 @@
           <t>yes (population_percentile, median_ratio)</t>
         </is>
       </c>
-      <c r="T3" s="15" t="inlineStr">
+      <c r="T3" s="14" t="inlineStr">
         <is>
           <t>DAHIL</t>
         </is>
@@ -1243,7 +1232,7 @@
           <t>seizure_amount_to_turnover</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>LAGGING_SELF</t>
         </is>
@@ -1318,7 +1307,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T4" s="17" t="inlineStr">
+      <c r="T4" s="16" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
@@ -1351,7 +1340,7 @@
           <t>check_payment_time_shift</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>RULE</t>
         </is>
@@ -1426,7 +1415,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T5" s="17" t="inlineStr">
+      <c r="T5" s="16" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
@@ -1459,7 +1448,7 @@
           <t>factoring_risk_presence</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>LAGGING_SELF</t>
         </is>
@@ -1534,7 +1523,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T6" s="17" t="inlineStr">
+      <c r="T6" s="16" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
@@ -1567,9 +1556,9 @@
           <t>bank_debt_to_ebitda</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>FAZ1</t>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>LEADING</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -1642,7 +1631,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T7" s="15" t="inlineStr">
+      <c r="T7" s="14" t="inlineStr">
         <is>
           <t>DAHIL</t>
         </is>
@@ -1675,9 +1664,9 @@
           <t>trade_receivables_to_turnover</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>FAZ1</t>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>LEADING</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -1750,7 +1739,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T8" s="15" t="inlineStr">
+      <c r="T8" s="14" t="inlineStr">
         <is>
           <t>DAHIL</t>
         </is>
@@ -1783,9 +1772,9 @@
           <t>profitability_to_turnover</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>FAZ1</t>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>LEADING</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1858,7 +1847,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T9" s="15" t="inlineStr">
+      <c r="T9" s="14" t="inlineStr">
         <is>
           <t>DAHIL</t>
         </is>
@@ -1891,7 +1880,7 @@
           <t>electricity_bill_amount_change</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>SEGMENT_SPECIFIC</t>
         </is>
@@ -1966,7 +1955,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T10" s="17" t="inlineStr">
+      <c r="T10" s="16" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
@@ -1999,7 +1988,7 @@
           <t>business_loan_vs_inflation</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>BIDIRECTIONAL_OR_JUDGMENT</t>
         </is>
@@ -2074,7 +2063,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T11" s="17" t="inlineStr">
+      <c r="T11" s="16" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
@@ -2107,9 +2096,9 @@
           <t>equity_change</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>FAZ1</t>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>LEADING</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -2182,7 +2171,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T12" s="15" t="inlineStr">
+      <c r="T12" s="14" t="inlineStr">
         <is>
           <t>DAHIL</t>
         </is>
@@ -2215,7 +2204,7 @@
           <t>delinquency_entry_or_frequency</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>LAGGING_SELF</t>
         </is>
@@ -2290,7 +2279,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T13" s="17" t="inlineStr">
+      <c r="T13" s="16" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
@@ -2323,7 +2312,7 @@
           <t>credit_card_full_payment_break</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>LAGGING_SELF</t>
         </is>
@@ -2398,7 +2387,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T14" s="17" t="inlineStr">
+      <c r="T14" s="16" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
@@ -2431,9 +2420,9 @@
           <t>ifrs9_behavioral_pd</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>FAZ1</t>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>LEADING</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -2506,7 +2495,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T15" s="15" t="inlineStr">
+      <c r="T15" s="14" t="inlineStr">
         <is>
           <t>DAHIL</t>
         </is>
@@ -2539,9 +2528,9 @@
           <t>kkb_commercial_score</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>FAZ1</t>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>LEADING</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -2614,7 +2603,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T16" s="15" t="inlineStr">
+      <c r="T16" s="14" t="inlineStr">
         <is>
           <t>DAHIL</t>
         </is>
@@ -2647,9 +2636,9 @@
           <t>kkb_indebtedness_index</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>FAZ1</t>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>LEADING</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -2722,7 +2711,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T17" s="15" t="inlineStr">
+      <c r="T17" s="14" t="inlineStr">
         <is>
           <t>DAHIL</t>
         </is>
@@ -2755,9 +2744,9 @@
           <t>net_sales_change</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>FAZ1</t>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>LEADING</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -2830,7 +2819,7 @@
           <t>yes (population_percentile, median_ratio)</t>
         </is>
       </c>
-      <c r="T18" s="15" t="inlineStr">
+      <c r="T18" s="14" t="inlineStr">
         <is>
           <t>DAHIL</t>
         </is>
@@ -2863,7 +2852,7 @@
           <t>memzuc_limit_change</t>
         </is>
       </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="E19" s="19" t="inlineStr">
         <is>
           <t>BIDIRECTIONAL_OR_JUDGMENT</t>
         </is>
@@ -2938,7 +2927,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T19" s="17" t="inlineStr">
+      <c r="T19" s="16" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
@@ -2971,7 +2960,7 @@
           <t>memzuc_bank_count_change</t>
         </is>
       </c>
-      <c r="E20" s="20" t="inlineStr">
+      <c r="E20" s="19" t="inlineStr">
         <is>
           <t>BIDIRECTIONAL_OR_JUDGMENT</t>
         </is>
@@ -3046,7 +3035,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T20" s="17" t="inlineStr">
+      <c r="T20" s="16" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
@@ -3079,7 +3068,7 @@
           <t>electricity_payment_failure</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>RULE</t>
         </is>
@@ -3154,7 +3143,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T21" s="17" t="inlineStr">
+      <c r="T21" s="16" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
@@ -3187,9 +3176,9 @@
           <t>kkb_check_portfolio_quality_deterioration</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>NARROW_SCOPE</t>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>COUNTERPARTY</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -3262,19 +3251,19 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T22" s="17" t="inlineStr">
+      <c r="T22" s="16" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>Metodoloji leading ama kapsam dar: sadece KKB cek raporu coverage'i olan musteriler.</t>
+          <t>Hamili/ciranta cekler musterinin elindeki baskasinin yazdigi cekler; ibrazda odeme orani azalmasi = kesideci (counterparty) odeyememis. Musterinin kendi olumsuzlugu degil.</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t>Genel kohort'un onemli bir parcasina uygulanamaz; Faz 1 kapsayici skorunda disarida.</t>
+          <t>Faz 1 'musterinin kendi leading sinyali' ilkesine uymuyor; ileri fazda counterparty alt modulune kaldirildi.</t>
         </is>
       </c>
     </row>
@@ -3295,9 +3284,9 @@
           <t>memzuc_limit_utilization_increase</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>FAZ1</t>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>LEADING</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -3370,7 +3359,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T23" s="15" t="inlineStr">
+      <c r="T23" s="14" t="inlineStr">
         <is>
           <t>DAHIL</t>
         </is>
@@ -3403,7 +3392,7 @@
           <t>livestock_count_change</t>
         </is>
       </c>
-      <c r="E24" s="19" t="inlineStr">
+      <c r="E24" s="18" t="inlineStr">
         <is>
           <t>SEGMENT_SPECIFIC</t>
         </is>
@@ -3478,7 +3467,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T24" s="17" t="inlineStr">
+      <c r="T24" s="16" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
@@ -3511,7 +3500,7 @@
           <t>issuer_adverse_to_receivables</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>COUNTERPARTY</t>
         </is>
@@ -3586,7 +3575,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T25" s="17" t="inlineStr">
+      <c r="T25" s="16" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
@@ -3619,7 +3608,7 @@
           <t>suspicious_receivables_to_receivables</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>COUNTERPARTY</t>
         </is>
@@ -3694,7 +3683,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T26" s="17" t="inlineStr">
+      <c r="T26" s="16" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
@@ -3727,7 +3716,7 @@
           <t>forward_check_to_notes_payable_ratio</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E27" s="15" t="inlineStr">
         <is>
           <t>LAGGING_SELF</t>
         </is>
@@ -3802,7 +3791,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T27" s="17" t="inlineStr">
+      <c r="T27" s="16" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
@@ -3835,7 +3824,7 @@
           <t>returned_check_note_ratio</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>COUNTERPARTY</t>
         </is>
@@ -3910,7 +3899,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T28" s="17" t="inlineStr">
+      <c r="T28" s="16" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
@@ -3943,9 +3932,9 @@
           <t>bank_asset_average_change</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
-        <is>
-          <t>NARROW_SCOPE</t>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>LEADING</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -4018,19 +4007,19 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T29" s="17" t="inlineStr">
+      <c r="T29" s="16" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t>Metodoloji leading (varlik azalmasi risk sinyali) ama olculen sadece bankamizdaki varlik; musterinin toplam varligi gorulemiyor (dar kapsam).</t>
+          <t>Leading: musterinin kendi bankamiz nezdindeki likidite/varlik sinyali. Buyuk banka konumumuz nedeniyle kapsama orani yuksek, narrow degil.</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t>Faz 1'de tam kapsamda anlamli sinyal uretemiyor; multi-bank tablosu olmadan bu metrik peer'lerle karsilastirilamaz.</t>
+          <t>Faz 1'e alinmadi: yon 'decrease_is_risk_but_ambiguous' (varlik azalmasi para baska yere aktarma ya da faaliyet kapanmasi olabilir) + PD / KKB / net_sales_change ile genis olcude ortusuyor, standalone marjinal katki dusuk.</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4040,7 @@
           <t>insurance_claim_to_receivables</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>COUNTERPARTY</t>
         </is>
@@ -4126,7 +4115,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="T30" s="17" t="inlineStr">
+      <c r="T30" s="16" t="inlineStr">
         <is>
           <t>DISI</t>
         </is>
@@ -4168,42 +4157,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Canonical Name</t>
         </is>
       </c>
-      <c r="C1" s="13" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>Formula</t>
         </is>
       </c>
-      <c r="E1" s="13" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>Business Heading</t>
         </is>
       </c>
-      <c r="F1" s="13" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>Yilliklastirma</t>
         </is>
       </c>
-      <c r="G1" s="13" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="H1" s="13" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>Missing Semantics</t>
         </is>
@@ -4213,7 +4202,7 @@
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>bank_debt_to_turnover</t>
         </is>
@@ -4253,7 +4242,7 @@
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>pos_volume_change</t>
         </is>
@@ -4293,7 +4282,7 @@
       <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>bank_debt_to_ebitda</t>
         </is>
@@ -4333,7 +4322,7 @@
       <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>trade_receivables_to_turnover</t>
         </is>
@@ -4373,7 +4362,7 @@
       <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>profitability_to_turnover</t>
         </is>
@@ -4413,7 +4402,7 @@
       <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>equity_change</t>
         </is>
@@ -4453,7 +4442,7 @@
       <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>ifrs9_behavioral_pd</t>
         </is>
@@ -4493,7 +4482,7 @@
       <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>kkb_commercial_score</t>
         </is>
@@ -4533,7 +4522,7 @@
       <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>kkb_indebtedness_index</t>
         </is>
@@ -4573,7 +4562,7 @@
       <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>net_sales_change</t>
         </is>
@@ -4613,7 +4602,7 @@
       <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>memzuc_limit_utilization_increase</t>
         </is>
@@ -4672,27 +4661,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Final Column</t>
         </is>
       </c>
-      <c r="C1" s="13" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>Column Type</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>Hesaplama / Donusum</t>
         </is>
       </c>
-      <c r="E1" s="13" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>Kaynak Business Heading</t>
         </is>
@@ -4702,12 +4691,12 @@
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>customer_id</t>
         </is>
       </c>
-      <c r="C2" s="24" t="inlineStr">
+      <c r="C2" s="22" t="inlineStr">
         <is>
           <t>technical_pass_through</t>
         </is>
@@ -4727,12 +4716,12 @@
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>snapshot_date</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>technical_pass_through</t>
         </is>
@@ -4752,12 +4741,12 @@
       <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>segment</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>technical_pass_through</t>
         </is>
@@ -4777,12 +4766,12 @@
       <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>bank_debt_to_turnover</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>derived_base</t>
         </is>
@@ -4802,12 +4791,12 @@
       <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>pos_volume_change</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>derived_base</t>
         </is>
@@ -4827,12 +4816,12 @@
       <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>bank_debt_to_ebitda</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>derived_base</t>
         </is>
@@ -4852,12 +4841,12 @@
       <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>trade_receivables_to_turnover</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>derived_base</t>
         </is>
@@ -4877,12 +4866,12 @@
       <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>profitability_to_turnover</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>derived_base</t>
         </is>
@@ -4902,12 +4891,12 @@
       <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>equity_change</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>derived_base</t>
         </is>
@@ -4927,12 +4916,12 @@
       <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>ifrs9_behavioral_pd</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>passthrough_base</t>
         </is>
@@ -4952,12 +4941,12 @@
       <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>kkb_commercial_score</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>passthrough_base</t>
         </is>
@@ -4977,12 +4966,12 @@
       <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>kkb_indebtedness_index</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>passthrough_base</t>
         </is>
@@ -5002,12 +4991,12 @@
       <c r="A14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>net_sales_change</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>derived_base</t>
         </is>
@@ -5027,12 +5016,12 @@
       <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>memzuc_limit_utilization_increase</t>
         </is>
       </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>derived_base</t>
         </is>
@@ -5052,12 +5041,12 @@
       <c r="A16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>bank_debt_to_turnover__delta_1</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5077,12 +5066,12 @@
       <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>bank_debt_to_turnover__self_zscore_6</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5102,12 +5091,12 @@
       <c r="A18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>pos_volume_change__delta_1</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5127,12 +5116,12 @@
       <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>pos_volume_change__self_zscore_6</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5152,12 +5141,12 @@
       <c r="A20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>bank_debt_to_ebitda__delta_1</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5177,12 +5166,12 @@
       <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>bank_debt_to_ebitda__self_zscore_6</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C21" s="24" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5202,12 +5191,12 @@
       <c r="A22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>trade_receivables_to_turnover__delta_1</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5227,12 +5216,12 @@
       <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>trade_receivables_to_turnover__self_zscore_6</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5252,12 +5241,12 @@
       <c r="A24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>profitability_to_turnover__delta_1</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C24" s="24" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5277,12 +5266,12 @@
       <c r="A25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>profitability_to_turnover__self_zscore_6</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
+      <c r="C25" s="24" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5302,12 +5291,12 @@
       <c r="A26" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>equity_change__delta_1</t>
         </is>
       </c>
-      <c r="C26" s="26" t="inlineStr">
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5327,12 +5316,12 @@
       <c r="A27" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>equity_change__self_zscore_6</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5352,12 +5341,12 @@
       <c r="A28" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>ifrs9_behavioral_pd__delta_1</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C28" s="24" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5377,12 +5366,12 @@
       <c r="A29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>ifrs9_behavioral_pd__self_zscore_6</t>
         </is>
       </c>
-      <c r="C29" s="26" t="inlineStr">
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5402,12 +5391,12 @@
       <c r="A30" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>kkb_commercial_score__delta_1</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
+      <c r="C30" s="24" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5427,12 +5416,12 @@
       <c r="A31" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>kkb_commercial_score__self_zscore_6</t>
         </is>
       </c>
-      <c r="C31" s="26" t="inlineStr">
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5452,12 +5441,12 @@
       <c r="A32" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>kkb_indebtedness_index__delta_1</t>
         </is>
       </c>
-      <c r="C32" s="26" t="inlineStr">
+      <c r="C32" s="24" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5477,12 +5466,12 @@
       <c r="A33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="23" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>kkb_indebtedness_index__self_zscore_6</t>
         </is>
       </c>
-      <c r="C33" s="26" t="inlineStr">
+      <c r="C33" s="24" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5502,12 +5491,12 @@
       <c r="A34" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="23" t="inlineStr">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>net_sales_change__delta_1</t>
         </is>
       </c>
-      <c r="C34" s="26" t="inlineStr">
+      <c r="C34" s="24" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5527,12 +5516,12 @@
       <c r="A35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="23" t="inlineStr">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>net_sales_change__self_zscore_6</t>
         </is>
       </c>
-      <c r="C35" s="26" t="inlineStr">
+      <c r="C35" s="24" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5552,12 +5541,12 @@
       <c r="A36" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="23" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>memzuc_limit_utilization_increase__delta_1</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="C36" s="24" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5577,12 +5566,12 @@
       <c r="A37" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="23" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>memzuc_limit_utilization_increase__self_zscore_6</t>
         </is>
       </c>
-      <c r="C37" s="26" t="inlineStr">
+      <c r="C37" s="24" t="inlineStr">
         <is>
           <t>self_history</t>
         </is>
@@ -5602,12 +5591,12 @@
       <c r="A38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="23" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>pos_volume_change__trend_slope_6</t>
         </is>
       </c>
-      <c r="C38" s="27" t="inlineStr">
+      <c r="C38" s="25" t="inlineStr">
         <is>
           <t>trend</t>
         </is>
@@ -5627,12 +5616,12 @@
       <c r="A39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="23" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>net_sales_change__trend_slope_6</t>
         </is>
       </c>
-      <c r="C39" s="27" t="inlineStr">
+      <c r="C39" s="25" t="inlineStr">
         <is>
           <t>trend</t>
         </is>
@@ -5652,12 +5641,12 @@
       <c r="A40" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="23" t="inlineStr">
+      <c r="B40" s="21" t="inlineStr">
         <is>
           <t>pos_volume_change__population_percentile</t>
         </is>
       </c>
-      <c r="C40" s="28" t="inlineStr">
+      <c r="C40" s="26" t="inlineStr">
         <is>
           <t>population_reference</t>
         </is>
@@ -5677,12 +5666,12 @@
       <c r="A41" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="23" t="inlineStr">
+      <c r="B41" s="21" t="inlineStr">
         <is>
           <t>pos_volume_change__vs_population_median_delta</t>
         </is>
       </c>
-      <c r="C41" s="28" t="inlineStr">
+      <c r="C41" s="26" t="inlineStr">
         <is>
           <t>population_reference</t>
         </is>
@@ -5702,12 +5691,12 @@
       <c r="A42" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="23" t="inlineStr">
+      <c r="B42" s="21" t="inlineStr">
         <is>
           <t>net_sales_change__population_percentile</t>
         </is>
       </c>
-      <c r="C42" s="28" t="inlineStr">
+      <c r="C42" s="26" t="inlineStr">
         <is>
           <t>population_reference</t>
         </is>
@@ -5727,12 +5716,12 @@
       <c r="A43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="23" t="inlineStr">
+      <c r="B43" s="21" t="inlineStr">
         <is>
           <t>net_sales_change__vs_population_median_delta</t>
         </is>
       </c>
-      <c r="C43" s="28" t="inlineStr">
+      <c r="C43" s="26" t="inlineStr">
         <is>
           <t>population_reference</t>
         </is>
@@ -5771,27 +5760,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Native Column</t>
         </is>
       </c>
-      <c r="C1" s="13" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>Aciklama</t>
         </is>
       </c>
-      <c r="E1" s="13" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>Hangi Derived Feature'i Besler</t>
         </is>
@@ -5801,7 +5790,7 @@
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>customer_id</t>
         </is>
@@ -5826,7 +5815,7 @@
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>snapshot_date</t>
         </is>
@@ -5851,7 +5840,7 @@
       <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>segment</t>
         </is>
@@ -5876,7 +5865,7 @@
       <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>is_balance_sheet_customer</t>
         </is>
@@ -5901,7 +5890,7 @@
       <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>has_pos</t>
         </is>
@@ -5926,7 +5915,7 @@
       <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>nace_section</t>
         </is>
@@ -5951,7 +5940,7 @@
       <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>nace_main</t>
         </is>
@@ -5976,7 +5965,7 @@
       <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>fs_period_code</t>
         </is>
@@ -6001,7 +5990,7 @@
       <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>fs_last_update_date</t>
         </is>
@@ -6026,7 +6015,7 @@
       <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>memzuc_total_cash_risk_0_24m</t>
         </is>
@@ -6051,7 +6040,7 @@
       <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>tlref_factor</t>
         </is>
@@ -6076,7 +6065,7 @@
       <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>fs_net_sales_cumulative</t>
         </is>
@@ -6101,7 +6090,7 @@
       <c r="A14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>fs_ebitda_cumulative</t>
         </is>
@@ -6126,7 +6115,7 @@
       <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>fs_trade_receivables</t>
         </is>
@@ -6151,7 +6140,7 @@
       <c r="A16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>fs_notes_receivable</t>
         </is>
@@ -6176,7 +6165,7 @@
       <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>fs_net_profit_cumulative</t>
         </is>
@@ -6201,7 +6190,7 @@
       <c r="A18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>fs_equity</t>
         </is>
@@ -6226,7 +6215,7 @@
       <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>pos_monthly_volume</t>
         </is>
@@ -6251,7 +6240,7 @@
       <c r="A20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>ifrs9_behavioral_pd</t>
         </is>
@@ -6276,7 +6265,7 @@
       <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>kkb_commercial_score</t>
         </is>
@@ -6301,7 +6290,7 @@
       <c r="A22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>kkb_indebtedness_index</t>
         </is>
@@ -6326,7 +6315,7 @@
       <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>memzuc_total_limit</t>
         </is>
@@ -6351,7 +6340,7 @@
       <c r="A24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>memzuc_total_risk</t>
         </is>
@@ -6387,7 +6376,7 @@
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="70" customWidth="1" min="4" max="4"/>
@@ -6395,444 +6384,444 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Canonical Name</t>
         </is>
       </c>
-      <c r="C1" s="13" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>Business Basligi</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>Kategori Gerekcesi</t>
         </is>
       </c>
-      <c r="E1" s="13" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>Secim Gerekcesi (Faz 1)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>LEADING</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>bank_asset_average_change</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Bankamizda Bulunan Mevduat / Varlik Ortalamalari</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Leading: musterinin kendi bankamiz nezdindeki likidite/varlik sinyali. Buyuk banka konumumuz nedeniyle kapsama orani yuksek, narrow degil.</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Faz 1'e alinmadi: yon 'decrease_is_risk_but_ambiguous' (varlik azalmasi para baska yere aktarma ya da faaliyet kapanmasi olabilir) + PD / KKB / net_sales_change ile genis olcude ortusuyor, standalone marjinal katki dusuk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>LAGGING_SELF</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>seizure_amount_to_turnover</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Haciz Tutari ve Ciro Iliskisi</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Musterinin kendi olumsuzlugu: devam eden haciz zaten yasanmis bir olay (self-lagging). Rule pattern'i 'ilk kez 24m' sadece companion filtredir.</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Kapsayici erken uyari skoruna katkisi sinirli; olay gerceklestikten sonra sinyal uretir. Faz 2'de rule katmaninda kullanilacak.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>LAGGING_SELF</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>factoring_risk_presence</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Faktoring</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Musterinin kendi faktoring kullanimi; olay zaten gerceklesmis (self-lagging).</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>3 ayri pattern kurali model degiskeni yerine rule katmaninda deger uretir; base feature olarak Faz 1'e alinmadi.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>LAGGING_SELF</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>delinquency_entry_or_frequency</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Musterinin Bankamizda veya Diger Bankalarda Gecikmeye Girme</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Musterinin kendi gecikme olayi zaten gerceklesmis; event-count lagging.</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Erken uyari skoru degil, gerceklesmis olumsuzluk sinyali; companion rule'lara birakildi.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>LAGGING_SELF</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>credit_card_full_payment_break</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Musterinin Bankamizdaki Kredi Karti Borcunun Tamamini Odememesi</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Musterinin kendi odememe olayi gerceklesmis; self-lagging.</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Olay sonrasi sinyal; Faz 1 kapsayici erken uyari skorunun disinda, rule katmaninda kullanilacak.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>LAGGING_SELF</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>forward_check_to_notes_payable_ratio</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>KKB Ileri Vadeli Cek ve Bilanco Senetli Borc / Verilen Cek Iliskisi</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Musterinin kendi ileri vadeli cek bindirmesi; '1 uzeri kosulu' esik kurali ile lagging bolgesine giriyor.</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Ham oran model degiskeni degil esik sonrasi rule olarak calisir; base feature olarak Faz 1'de tutulmadi.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>COUNTERPARTY</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>kkb_check_portfolio_quality_deterioration</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>KKB Cek Portfoy Kalitesinde Bozulma</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Hamili/ciranta cekler musterinin elindeki baskasinin yazdigi cekler; ibrazda odeme orani azalmasi = kesideci (counterparty) odeyememis. Musterinin kendi olumsuzlugu degil.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Faz 1 'musterinin kendi leading sinyali' ilkesine uymuyor; ileri fazda counterparty alt modulune kaldirildi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>COUNTERPARTY</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>issuer_adverse_to_receivables</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Kesideci Olumsuzlugu ve Bilanco Ticari Alacak Iliskisi</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Musterinin kendi olumsuzlugu degil: musterinin elindeki cekin kesidecisi (counterparty) olumsuzluk yasamis.</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Counterparty risk sinyali; Faz 1 kapsayici 'musteri kendi leading' ilkesinin disinda. Gelecekte counterparty alt modulune gider.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>COUNTERPARTY</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>suspicious_receivables_to_receivables</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Supheli Ticari Alacaklar ve Ticari Alacak Iliskisi</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Musterinin kendi alacagi supheli; yani alici (counterparty) odeyemedigi icin bilancoda ayrilmis. Musterinin bizzat leading sinyali degil.</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Faz 1'de disarida; counterparty risk bilesenini ileri faz alt modulune erteledik.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="22" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>COUNTERPARTY</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>returned_check_note_ratio</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Bankamizdaki Cek/Senet Iade Orani</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Musterinin bankamiza tahsil icin verdigi cekler/senetler iade olmus; kesideci (counterparty) odeyememis. Musterinin kendi olayi degil.</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Counterparty risk; Faz 1 kapsayici 'musteri kendi leading' skoruna katki tutumlu. Ileri fazda ayri modul.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>COUNTERPARTY</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>insurance_claim_to_receivables</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Alacak Sigortasi Tazmin Verisi ve Bilanco Ticari Alacak Iliskisi</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Musterinin kendi olumsuzlugu degil: musterinin alicisi odeyemedigi icin sigorta sirketi tazmin yapmis. Counterparty risk sinyali.</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Ek olarak %15 alti filter rule; Faz 1 kapsayici 'musteri kendi leading' ilkesine uymuyor, ileri faz counterparty modulune kaldirildi.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>RULE</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>check_payment_time_shift</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Cek Odemesi Zamani</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Tam pattern kurgusu: 'son 6 ayda ilk kez ogleden sonra', 'son 3 ayda pes pese farkli gun'. Modele girecek surekli oran/indikator yok, sadece deterministic event pattern'leri.</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Modelleme degiskeni olamaz (tek sayisi/orani yok); rule katmaninda companion olarak calisir.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>RULE</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>electricity_payment_failure</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Elektrik Borcunu Odeyemeyenler</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Tam pattern kurali: 'son 2 yilda ilk kez gec odeme', 'son 1 yilda 2 kez pes pese'. Modele girecek surekli bir metrik yok. Ek kisitlayici: elektrik abonesi alt evreni.</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Rule katmanina birakildi; Faz 1 kapsayici genel skorun disinda.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>SEGMENT_SPECIFIC</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>electricity_bill_amount_change</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Musterinin Aylik Elektrik Fatura Tutarlari (NACE imalat)</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Yalniz NACE section C (imalat) icin tanimli; genel kohorta uygulanamaz.</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Faz 1 kapsayici skora giremez; ileri fazda imalat alt modelinin feature'i olur.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>SEGMENT_SPECIFIC</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>livestock_count_change</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Hayvan Sayisi</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Yalniz Tarim-Hayvancilik alt segmenti; Faz 1 ana kohortunda applicability yok.</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Ileri fazda Tarim alt modelinde kullanilir; Faz 1'de kapsam disi.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="21" t="inlineStr">
-        <is>
-          <t>NARROW_SCOPE</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>kkb_check_portfolio_quality_deterioration</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>KKB Cek Portfoy Kalitesinde Bozulma</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Metodoloji leading ama kapsam dar: sadece KKB cek raporu coverage'i olan musteriler.</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Genel kohort'un onemli bir parcasina uygulanamaz; Faz 1 kapsayici skorunda disarida.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="21" t="inlineStr">
-        <is>
-          <t>NARROW_SCOPE</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>bank_asset_average_change</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Bankamizda Bulunan Mevduat / Varlik Ortalamalari</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Metodoloji leading (varlik azalmasi risk sinyali) ama olculen sadece bankamizdaki varlik; musterinin toplam varligi gorulemiyor (dar kapsam).</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Faz 1'de tam kapsamda anlamli sinyal uretemiyor; multi-bank tablosu olmadan bu metrik peer'lerle karsilastirilamaz.</t>
-        </is>
-      </c>
-    </row>
     <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>BIDIRECTIONAL_OR_JUDGMENT</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>business_loan_vs_inflation</t>
         </is>
@@ -6854,12 +6843,12 @@
       </c>
     </row>
     <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>BIDIRECTIONAL_OR_JUDGMENT</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>memzuc_limit_change</t>
         </is>
@@ -6881,12 +6870,12 @@
       </c>
     </row>
     <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>BIDIRECTIONAL_OR_JUDGMENT</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>memzuc_bank_count_change</t>
         </is>

--- a/dictionary/faz1_variable_dictionary.xlsx
+++ b/dictionary/faz1_variable_dictionary.xlsx
@@ -599,6 +599,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -643,7 +644,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>11 (hepsi LEADING kategorisinden)</t>
+          <t>11 (hepsi LEADING kategorisinden; bank_asset_average_change ve forward_check_to_notes_payable_ratio LEADING ama DISI)</t>
         </is>
       </c>
     </row>
@@ -703,7 +704,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>LEADING, LAGGING_SELF, COUNTERPARTY, RULE, SEGMENT_SPECIFIC, BIDIRECTIONAL_OR_JUDGMENT</t>
+          <t>LEADING, LAGGING_SELF, COUNTERPARTY, RULE, SEGMENT_SPECIFIC, BIDIRECTIONAL_OR_JUDGMENT (hiyerarsik karar: SEGMENT_SPECIFIC &gt; COUNTERPARTY &gt; RULE &gt; LAGGING_SELF &gt; BIDIRECTIONAL_OR_JUDGMENT &gt; LEADING)</t>
         </is>
       </c>
     </row>
@@ -715,7 +716,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Kategori = degiskenin dogasi. Faz 1 Karari (DAHIL/DISI) ayri bir secimdir: bir degisken LEADING olup Faz 1 disinda kalabilir.</t>
+          <t>Kategori = degiskenin dogasi; hiyerarsi dominant eleme sebebine gore tek kategori atar. Faz 1 Karari (DAHIL/DISI) ayri bir secimdir: bir degisken LEADING olup Faz 1 disinda kalabilir (ornek: bank_asset_average_change, forward_check_to_notes_payable_ratio).</t>
         </is>
       </c>
     </row>
@@ -767,6 +768,8 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
@@ -3068,9 +3071,9 @@
           <t>electricity_payment_failure</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>RULE</t>
+      <c r="E21" s="18" t="inlineStr">
+        <is>
+          <t>SEGMENT_SPECIFIC</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -3150,12 +3153,12 @@
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t>Tam pattern kurali: 'son 2 yilda ilk kez gec odeme', 'son 1 yilda 2 kez pes pese'. Modele girecek surekli bir metrik yok. Ek kisitlayici: elektrik abonesi alt evreni.</t>
+          <t>Elektrik abonesi alt evreni feature'in tanimli oldugu tek kesim; genel kohortta NA. Event count + 2 pattern (ilk kez 24m, pes pese 2m) de bulunuyor ama asil eleme sebebi dar alt evren (hiyerarsik karar).</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t>Rule katmanina birakildi; Faz 1 kapsayici genel skorun disinda.</t>
+          <t>Faz 1 kapsayici 'bilancolu + POS yogun' kohortunda uygulanabilir degil; ileri fazda elektrik-abonesi alt modulunde event + pattern rule katmaninda kullanilir.</t>
         </is>
       </c>
     </row>
@@ -3716,9 +3719,9 @@
           <t>forward_check_to_notes_payable_ratio</t>
         </is>
       </c>
-      <c r="E27" s="15" t="inlineStr">
-        <is>
-          <t>LAGGING_SELF</t>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>LEADING</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -3798,12 +3801,12 @@
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t>Musterinin kendi ileri vadeli cek bindirmesi; '1 uzeri kosulu' esik kurali ile lagging bolgesine giriyor.</t>
+          <t>Leading: metrik ileri vadeli cek / (senetli borc + verilen cek); musterinin gelecekteki odeme yukunu bilanco yukumlulukleri ile olcen surekli bir oran. Olay gerceklesmemis, kaldirac/basinc on-sinyali.</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t>Ham oran model degiskeni degil esik sonrasi rule olarak calisir; base feature olarak Faz 1'de tutulmadi.</t>
+          <t>Faz 1 DISI: applicability 'cek/senet yogun musteri' dar kapsam; is birimi metrigi '1 uzeri kosuluyla' kullanmayi onerdigi icin ham oran yerine esik rule'u (forward_check_above_1_flag) companion layer'a alindi.</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6414,7 @@
       </c>
     </row>
     <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>LEADING</t>
         </is>
@@ -6438,277 +6441,277 @@
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>LEADING</t>
+        </is>
+      </c>
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t>forward_check_to_notes_payable_ratio</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>KKB Ileri Vadeli Cek ve Bilanco Senetli Borc / Verilen Cek Iliskisi</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Leading: metrik ileri vadeli cek / (senetli borc + verilen cek); musterinin gelecekteki odeme yukunu bilanco yukumlulukleri ile olcen surekli bir oran. Olay gerceklesmemis, kaldirac/basinc on-sinyali.</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Faz 1 DISI: applicability 'cek/senet yogun musteri' dar kapsam; is birimi metrigi '1 uzeri kosuluyla' kullanmayi onerdigi icin ham oran yerine esik rule'u (forward_check_above_1_flag) companion layer'a alindi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>LAGGING_SELF</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>credit_card_full_payment_break</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Musterinin Bankamizdaki Kredi Karti Borcunun Tamamini Odememesi</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Musterinin kendi odememe olayi gerceklesmis; self-lagging.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Olay sonrasi sinyal; Faz 1 kapsayici erken uyari skorunun disinda, rule katmaninda kullanilacak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>LAGGING_SELF</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>delinquency_entry_or_frequency</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Musterinin Bankamizda veya Diger Bankalarda Gecikmeye Girme</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Musterinin kendi gecikme olayi zaten gerceklesmis; event-count lagging.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Erken uyari skoru degil, gerceklesmis olumsuzluk sinyali; companion rule'lara birakildi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>LAGGING_SELF</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>factoring_risk_presence</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Faktoring</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Musterinin kendi faktoring kullanimi; olay zaten gerceklesmis (self-lagging).</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>3 ayri pattern kurali model degiskeni yerine rule katmaninda deger uretir; base feature olarak Faz 1'e alinmadi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>LAGGING_SELF</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>seizure_amount_to_turnover</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Haciz Tutari ve Ciro Iliskisi</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Musterinin kendi olumsuzlugu: devam eden haciz zaten yasanmis bir olay (self-lagging). Rule pattern'i 'ilk kez 24m' sadece companion filtredir.</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Kapsayici erken uyari skoruna katkisi sinirli; olay gerceklestikten sonra sinyal uretir. Faz 2'de rule katmaninda kullanilacak.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>LAGGING_SELF</t>
-        </is>
-      </c>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t>factoring_risk_presence</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Faktoring</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Musterinin kendi faktoring kullanimi; olay zaten gerceklesmis (self-lagging).</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>3 ayri pattern kurali model degiskeni yerine rule katmaninda deger uretir; base feature olarak Faz 1'e alinmadi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>LAGGING_SELF</t>
-        </is>
-      </c>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t>delinquency_entry_or_frequency</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Musterinin Bankamizda veya Diger Bankalarda Gecikmeye Girme</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Musterinin kendi gecikme olayi zaten gerceklesmis; event-count lagging.</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Erken uyari skoru degil, gerceklesmis olumsuzluk sinyali; companion rule'lara birakildi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>LAGGING_SELF</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>credit_card_full_payment_break</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Musterinin Bankamizdaki Kredi Karti Borcunun Tamamini Odememesi</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Musterinin kendi odememe olayi gerceklesmis; self-lagging.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Olay sonrasi sinyal; Faz 1 kapsayici erken uyari skorunun disinda, rule katmaninda kullanilacak.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>LAGGING_SELF</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>forward_check_to_notes_payable_ratio</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>KKB Ileri Vadeli Cek ve Bilanco Senetli Borc / Verilen Cek Iliskisi</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Musterinin kendi ileri vadeli cek bindirmesi; '1 uzeri kosulu' esik kurali ile lagging bolgesine giriyor.</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Ham oran model degiskeni degil esik sonrasi rule olarak calisir; base feature olarak Faz 1'de tutulmadi.</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>COUNTERPARTY</t>
         </is>
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
+          <t>insurance_claim_to_receivables</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Alacak Sigortasi Tazmin Verisi ve Bilanco Ticari Alacak Iliskisi</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Musterinin kendi olumsuzlugu degil: musterinin alicisi odeyemedigi icin sigorta sirketi tazmin yapmis. Counterparty risk sinyali.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Ek olarak %15 alti filter rule; Faz 1 kapsayici 'musteri kendi leading' ilkesine uymuyor, ileri faz counterparty modulune kaldirildi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>COUNTERPARTY</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>issuer_adverse_to_receivables</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Kesideci Olumsuzlugu ve Bilanco Ticari Alacak Iliskisi</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Musterinin kendi olumsuzlugu degil: musterinin elindeki cekin kesidecisi (counterparty) olumsuzluk yasamis.</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Counterparty risk sinyali; Faz 1 kapsayici 'musteri kendi leading' ilkesinin disinda. Gelecekte counterparty alt modulune gider.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>COUNTERPARTY</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
           <t>kkb_check_portfolio_quality_deterioration</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>KKB Cek Portfoy Kalitesinde Bozulma</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Hamili/ciranta cekler musterinin elindeki baskasinin yazdigi cekler; ibrazda odeme orani azalmasi = kesideci (counterparty) odeyememis. Musterinin kendi olumsuzlugu degil.</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Faz 1 'musterinin kendi leading sinyali' ilkesine uymuyor; ileri fazda counterparty alt modulune kaldirildi.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>COUNTERPARTY</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>issuer_adverse_to_receivables</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Kesideci Olumsuzlugu ve Bilanco Ticari Alacak Iliskisi</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Musterinin kendi olumsuzlugu degil: musterinin elindeki cekin kesidecisi (counterparty) olumsuzluk yasamis.</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Counterparty risk sinyali; Faz 1 kapsayici 'musteri kendi leading' ilkesinin disinda. Gelecekte counterparty alt modulune gider.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>returned_check_note_ratio</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Bankamizdaki Cek/Senet Iade Orani</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Musterinin bankamiza tahsil icin verdigi cekler/senetler iade olmus; kesideci (counterparty) odeyememis. Musterinin kendi olayi degil.</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Counterparty risk; Faz 1 kapsayici 'musteri kendi leading' skoruna katki tutumlu. Ileri fazda ayri modul.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>COUNTERPARTY</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>suspicious_receivables_to_receivables</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Supheli Ticari Alacaklar ve Ticari Alacak Iliskisi</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Musterinin kendi alacagi supheli; yani alici (counterparty) odeyemedigi icin bilancoda ayrilmis. Musterinin bizzat leading sinyali degil.</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Faz 1'de disarida; counterparty risk bilesenini ileri faz alt modulune erteledik.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>COUNTERPARTY</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>returned_check_note_ratio</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Bankamizdaki Cek/Senet Iade Orani</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Musterinin bankamiza tahsil icin verdigi cekler/senetler iade olmus; kesideci (counterparty) odeyememis. Musterinin kendi olayi degil.</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Counterparty risk; Faz 1 kapsayici 'musteri kendi leading' skoruna katki tutumlu. Ileri fazda ayri modul.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>COUNTERPARTY</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>insurance_claim_to_receivables</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Alacak Sigortasi Tazmin Verisi ve Bilanco Ticari Alacak Iliskisi</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Musterinin kendi olumsuzlugu degil: musterinin alicisi odeyemedigi icin sigorta sirketi tazmin yapmis. Counterparty risk sinyali.</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Ek olarak %15 alti filter rule; Faz 1 kapsayici 'musteri kendi leading' ilkesine uymuyor, ileri faz counterparty modulune kaldirildi.</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>RULE</t>
         </is>
@@ -6735,65 +6738,65 @@
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>RULE</t>
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>SEGMENT_SPECIFIC</t>
         </is>
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
+          <t>electricity_bill_amount_change</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Musterinin Aylik Elektrik Fatura Tutarlari (NACE imalat)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Yalniz NACE section C (imalat) icin tanimli; genel kohorta uygulanamaz.</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Faz 1 kapsayici skora giremez; ileri fazda imalat alt modelinin feature'i olur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>SEGMENT_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
           <t>electricity_payment_failure</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Elektrik Borcunu Odeyemeyenler</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Tam pattern kurali: 'son 2 yilda ilk kez gec odeme', 'son 1 yilda 2 kez pes pese'. Modele girecek surekli bir metrik yok. Ek kisitlayici: elektrik abonesi alt evreni.</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Rule katmanina birakildi; Faz 1 kapsayici genel skorun disinda.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Elektrik abonesi alt evreni feature'in tanimli oldugu tek kesim; genel kohortta NA. Event count + 2 pattern (ilk kez 24m, pes pese 2m) de bulunuyor ama asil eleme sebebi dar alt evren (hiyerarsik karar).</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Faz 1 kapsayici 'bilancolu + POS yogun' kohortunda uygulanabilir degil; ileri fazda elektrik-abonesi alt modulunde event + pattern rule katmaninda kullanilir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>SEGMENT_SPECIFIC</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
-        <is>
-          <t>electricity_bill_amount_change</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Musterinin Aylik Elektrik Fatura Tutarlari (NACE imalat)</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Yalniz NACE section C (imalat) icin tanimli; genel kohorta uygulanamaz.</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Faz 1 kapsayici skora giremez; ileri fazda imalat alt modelinin feature'i olur.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>SEGMENT_SPECIFIC</t>
-        </is>
-      </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
           <t>livestock_count_change</t>
@@ -6816,7 +6819,7 @@
       </c>
     </row>
     <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>BIDIRECTIONAL_OR_JUDGMENT</t>
         </is>
@@ -6843,56 +6846,56 @@
       </c>
     </row>
     <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>BIDIRECTIONAL_OR_JUDGMENT</t>
         </is>
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
+          <t>memzuc_bank_count_change</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Memzuc Banka Sayisi Azalisi</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Bidirectional: banka sayisi azalmasi kredibilite dusuklugu de olabilir, borc toplanmasi da olabilir.</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Yon belirsizligi nedeniyle kapsayici skora katkisi guvenli degil; Faz 1 disinda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>BIDIRECTIONAL_OR_JUDGMENT</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
           <t>memzuc_limit_change</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Memzuc Limit Azalisi</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Bidirectional: limit azalisi iyi (risk dustu) veya kotu (banka limiti kisiyor) anlamina gelebilir; deterministic yon yok.</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Standardize yon olmadan Faz 1 kapsayici skoruna katkisiz; rule/insight olarak ayri kullanilabilir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>BIDIRECTIONAL_OR_JUDGMENT</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t>memzuc_bank_count_change</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Memzuc Banka Sayisi Azalisi</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Bidirectional: banka sayisi azalmasi kredibilite dusuklugu de olabilir, borc toplanmasi da olabilir.</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Yon belirsizligi nedeniyle kapsayici skora katkisi guvenli degil; Faz 1 disinda.</t>
         </is>
       </c>
     </row>

--- a/dictionary/faz1_variable_dictionary.xlsx
+++ b/dictionary/faz1_variable_dictionary.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>11 (hepsi LEADING kategorisinden; bank_asset_average_change ve forward_check_to_notes_payable_ratio LEADING ama DISI)</t>
+          <t>11 (hepsi LEADING kategorisinden; ayrica 3 LEADING DISI: bank_asset_average_change, forward_check_to_notes_payable_ratio, business_loan_vs_inflation)</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Kategori = degiskenin dogasi; hiyerarsi dominant eleme sebebine gore tek kategori atar. Faz 1 Karari (DAHIL/DISI) ayri bir secimdir: bir degisken LEADING olup Faz 1 disinda kalabilir (ornek: bank_asset_average_change, forward_check_to_notes_payable_ratio).</t>
+          <t>Kategori = degiskenin dogasi; hiyerarsi dominant eleme sebebine gore tek kategori atar. Faz 1 Karari (DAHIL/DISI) ayri bir secimdir: bir degisken LEADING olup Faz 1 disinda kalabilir (bank_asset_average_change, forward_check_to_notes_payable_ratio, business_loan_vs_inflation bu duruma ornektir).</t>
         </is>
       </c>
     </row>
@@ -1991,9 +1991,9 @@
           <t>business_loan_vs_inflation</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>BIDIRECTIONAL_OR_JUDGMENT</t>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>LEADING</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>Yargi gerektiriyor: 'enflasyon uyumlu buyume kotu degil' ifadesi deterministic bir oran/esik halinde olculmuyor.</t>
+          <t>Leading: musterinin memzuc 0-12 ay ve 12-24 ay nakdi kredilerinin buyume hizi; tek yonlu (artis kotu). BIDIRECTIONAL degil, yon net - sadece bir judgment filter'i var (enflasyon uyumlu artis risk degildir).</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>Standardize edilemedigi icin Faz 1 genel kapsayici skora alinmadi; business team ek kural tanimlamali.</t>
+          <t>Faz 1 DISI: ana metrik leading (kredi buyume hizi) ama is birimi 'enflasyon uyumlu artis risk degildir' yargisini deterministic oran/esik ile ifade etmiyor; enflasyon-adjust rule olmadan standalone skora katki riski var. Judgment filter rule olgunlastiktan sonra leading base setine alinabilir.</t>
         </is>
       </c>
     </row>
@@ -6448,49 +6448,49 @@
       </c>
       <c r="B3" s="21" t="inlineStr">
         <is>
+          <t>business_loan_vs_inflation</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Musterinin Bankalardaki Isletme Borclari ve Enflasyon Iliskisi</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Leading: musterinin memzuc 0-12 ay ve 12-24 ay nakdi kredilerinin buyume hizi; tek yonlu (artis kotu). BIDIRECTIONAL degil, yon net - sadece bir judgment filter'i var (enflasyon uyumlu artis risk degildir).</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Faz 1 DISI: ana metrik leading (kredi buyume hizi) ama is birimi 'enflasyon uyumlu artis risk degildir' yargisini deterministic oran/esik ile ifade etmiyor; enflasyon-adjust rule olmadan standalone skora katki riski var. Judgment filter rule olgunlastiktan sonra leading base setine alinabilir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>LEADING</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
           <t>forward_check_to_notes_payable_ratio</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>KKB Ileri Vadeli Cek ve Bilanco Senetli Borc / Verilen Cek Iliskisi</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Leading: metrik ileri vadeli cek / (senetli borc + verilen cek); musterinin gelecekteki odeme yukunu bilanco yukumlulukleri ile olcen surekli bir oran. Olay gerceklesmemis, kaldirac/basinc on-sinyali.</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Faz 1 DISI: applicability 'cek/senet yogun musteri' dar kapsam; is birimi metrigi '1 uzeri kosuluyla' kullanmayi onerdigi icin ham oran yerine esik rule'u (forward_check_above_1_flag) companion layer'a alindi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>LAGGING_SELF</t>
-        </is>
-      </c>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t>credit_card_full_payment_break</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Musterinin Bankamizdaki Kredi Karti Borcunun Tamamini Odememesi</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Musterinin kendi odememe olayi gerceklesmis; self-lagging.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Olay sonrasi sinyal; Faz 1 kapsayici erken uyari skorunun disinda, rule katmaninda kullanilacak.</t>
         </is>
       </c>
     </row>
@@ -6502,22 +6502,22 @@
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>delinquency_entry_or_frequency</t>
+          <t>credit_card_full_payment_break</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Musterinin Bankamizda veya Diger Bankalarda Gecikmeye Girme</t>
+          <t>Musterinin Bankamizdaki Kredi Karti Borcunun Tamamini Odememesi</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Musterinin kendi gecikme olayi zaten gerceklesmis; event-count lagging.</t>
+          <t>Musterinin kendi odememe olayi gerceklesmis; self-lagging.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Erken uyari skoru degil, gerceklesmis olumsuzluk sinyali; companion rule'lara birakildi.</t>
+          <t>Olay sonrasi sinyal; Faz 1 kapsayici erken uyari skorunun disinda, rule katmaninda kullanilacak.</t>
         </is>
       </c>
     </row>
@@ -6529,22 +6529,22 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>factoring_risk_presence</t>
+          <t>delinquency_entry_or_frequency</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Faktoring</t>
+          <t>Musterinin Bankamizda veya Diger Bankalarda Gecikmeye Girme</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Musterinin kendi faktoring kullanimi; olay zaten gerceklesmis (self-lagging).</t>
+          <t>Musterinin kendi gecikme olayi zaten gerceklesmis; event-count lagging.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>3 ayri pattern kurali model degiskeni yerine rule katmaninda deger uretir; base feature olarak Faz 1'e alinmadi.</t>
+          <t>Erken uyari skoru degil, gerceklesmis olumsuzluk sinyali; companion rule'lara birakildi.</t>
         </is>
       </c>
     </row>
@@ -6556,49 +6556,49 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
+          <t>factoring_risk_presence</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Faktoring</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Musterinin kendi faktoring kullanimi; olay zaten gerceklesmis (self-lagging).</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>3 ayri pattern kurali model degiskeni yerine rule katmaninda deger uretir; base feature olarak Faz 1'e alinmadi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>LAGGING_SELF</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
           <t>seizure_amount_to_turnover</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Haciz Tutari ve Ciro Iliskisi</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Musterinin kendi olumsuzlugu: devam eden haciz zaten yasanmis bir olay (self-lagging). Rule pattern'i 'ilk kez 24m' sadece companion filtredir.</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Kapsayici erken uyari skoruna katkisi sinirli; olay gerceklestikten sonra sinyal uretir. Faz 2'de rule katmaninda kullanilacak.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>COUNTERPARTY</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>insurance_claim_to_receivables</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Alacak Sigortasi Tazmin Verisi ve Bilanco Ticari Alacak Iliskisi</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Musterinin kendi olumsuzlugu degil: musterinin alicisi odeyemedigi icin sigorta sirketi tazmin yapmis. Counterparty risk sinyali.</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Ek olarak %15 alti filter rule; Faz 1 kapsayici 'musteri kendi leading' ilkesine uymuyor, ileri faz counterparty modulune kaldirildi.</t>
         </is>
       </c>
     </row>
@@ -6610,22 +6610,22 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>issuer_adverse_to_receivables</t>
+          <t>insurance_claim_to_receivables</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Kesideci Olumsuzlugu ve Bilanco Ticari Alacak Iliskisi</t>
+          <t>Alacak Sigortasi Tazmin Verisi ve Bilanco Ticari Alacak Iliskisi</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Musterinin kendi olumsuzlugu degil: musterinin elindeki cekin kesidecisi (counterparty) olumsuzluk yasamis.</t>
+          <t>Musterinin kendi olumsuzlugu degil: musterinin alicisi odeyemedigi icin sigorta sirketi tazmin yapmis. Counterparty risk sinyali.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Counterparty risk sinyali; Faz 1 kapsayici 'musteri kendi leading' ilkesinin disinda. Gelecekte counterparty alt modulune gider.</t>
+          <t>Ek olarak %15 alti filter rule; Faz 1 kapsayici 'musteri kendi leading' ilkesine uymuyor, ileri faz counterparty modulune kaldirildi.</t>
         </is>
       </c>
     </row>
@@ -6637,22 +6637,22 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>kkb_check_portfolio_quality_deterioration</t>
+          <t>issuer_adverse_to_receivables</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>KKB Cek Portfoy Kalitesinde Bozulma</t>
+          <t>Kesideci Olumsuzlugu ve Bilanco Ticari Alacak Iliskisi</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Hamili/ciranta cekler musterinin elindeki baskasinin yazdigi cekler; ibrazda odeme orani azalmasi = kesideci (counterparty) odeyememis. Musterinin kendi olumsuzlugu degil.</t>
+          <t>Musterinin kendi olumsuzlugu degil: musterinin elindeki cekin kesidecisi (counterparty) olumsuzluk yasamis.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Faz 1 'musterinin kendi leading sinyali' ilkesine uymuyor; ileri fazda counterparty alt modulune kaldirildi.</t>
+          <t>Counterparty risk sinyali; Faz 1 kapsayici 'musteri kendi leading' ilkesinin disinda. Gelecekte counterparty alt modulune gider.</t>
         </is>
       </c>
     </row>
@@ -6664,22 +6664,22 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>returned_check_note_ratio</t>
+          <t>kkb_check_portfolio_quality_deterioration</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Bankamizdaki Cek/Senet Iade Orani</t>
+          <t>KKB Cek Portfoy Kalitesinde Bozulma</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Musterinin bankamiza tahsil icin verdigi cekler/senetler iade olmus; kesideci (counterparty) odeyememis. Musterinin kendi olayi degil.</t>
+          <t>Hamili/ciranta cekler musterinin elindeki baskasinin yazdigi cekler; ibrazda odeme orani azalmasi = kesideci (counterparty) odeyememis. Musterinin kendi olumsuzlugu degil.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Counterparty risk; Faz 1 kapsayici 'musteri kendi leading' skoruna katki tutumlu. Ileri fazda ayri modul.</t>
+          <t>Faz 1 'musterinin kendi leading sinyali' ilkesine uymuyor; ileri fazda counterparty alt modulune kaldirildi.</t>
         </is>
       </c>
     </row>
@@ -6691,76 +6691,76 @@
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
+          <t>returned_check_note_ratio</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Bankamizdaki Cek/Senet Iade Orani</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Musterinin bankamiza tahsil icin verdigi cekler/senetler iade olmus; kesideci (counterparty) odeyememis. Musterinin kendi olayi degil.</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Counterparty risk; Faz 1 kapsayici 'musteri kendi leading' skoruna katki tutumlu. Ileri fazda ayri modul.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>COUNTERPARTY</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
           <t>suspicious_receivables_to_receivables</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Supheli Ticari Alacaklar ve Ticari Alacak Iliskisi</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Musterinin kendi alacagi supheli; yani alici (counterparty) odeyemedigi icin bilancoda ayrilmis. Musterinin bizzat leading sinyali degil.</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Faz 1'de disarida; counterparty risk bilesenini ileri faz alt modulune erteledik.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>RULE</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>check_payment_time_shift</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Cek Odemesi Zamani</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Tam pattern kurgusu: 'son 6 ayda ilk kez ogleden sonra', 'son 3 ayda pes pese farkli gun'. Modele girecek surekli oran/indikator yok, sadece deterministic event pattern'leri.</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Modelleme degiskeni olamaz (tek sayisi/orani yok); rule katmaninda companion olarak calisir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>SEGMENT_SPECIFIC</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>electricity_bill_amount_change</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Musterinin Aylik Elektrik Fatura Tutarlari (NACE imalat)</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Yalniz NACE section C (imalat) icin tanimli; genel kohorta uygulanamaz.</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Faz 1 kapsayici skora giremez; ileri fazda imalat alt modelinin feature'i olur.</t>
         </is>
       </c>
     </row>
@@ -6772,22 +6772,22 @@
       </c>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t>electricity_payment_failure</t>
+          <t>electricity_bill_amount_change</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Elektrik Borcunu Odeyemeyenler</t>
+          <t>Musterinin Aylik Elektrik Fatura Tutarlari (NACE imalat)</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Elektrik abonesi alt evreni feature'in tanimli oldugu tek kesim; genel kohortta NA. Event count + 2 pattern (ilk kez 24m, pes pese 2m) de bulunuyor ama asil eleme sebebi dar alt evren (hiyerarsik karar).</t>
+          <t>Yalniz NACE section C (imalat) icin tanimli; genel kohorta uygulanamaz.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Faz 1 kapsayici 'bilancolu + POS yogun' kohortunda uygulanabilir degil; ileri fazda elektrik-abonesi alt modulunde event + pattern rule katmaninda kullanilir.</t>
+          <t>Faz 1 kapsayici skora giremez; ileri fazda imalat alt modelinin feature'i olur.</t>
         </is>
       </c>
     </row>
@@ -6799,49 +6799,49 @@
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
+          <t>electricity_payment_failure</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Elektrik Borcunu Odeyemeyenler</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Elektrik abonesi alt evreni feature'in tanimli oldugu tek kesim; genel kohortta NA. Event count + 2 pattern (ilk kez 24m, pes pese 2m) de bulunuyor ama asil eleme sebebi dar alt evren (hiyerarsik karar).</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Faz 1 kapsayici 'bilancolu + POS yogun' kohortunda uygulanabilir degil; ileri fazda elektrik-abonesi alt modulunde event + pattern rule katmaninda kullanilir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>SEGMENT_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
           <t>livestock_count_change</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Hayvan Sayisi</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Yalniz Tarim-Hayvancilik alt segmenti; Faz 1 ana kohortunda applicability yok.</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Ileri fazda Tarim alt modelinde kullanilir; Faz 1'de kapsam disi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>BIDIRECTIONAL_OR_JUDGMENT</t>
-        </is>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>business_loan_vs_inflation</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Musterinin Bankalardaki Isletme Borclari ve Enflasyon Iliskisi</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Yargi gerektiriyor: 'enflasyon uyumlu buyume kotu degil' ifadesi deterministic bir oran/esik halinde olculmuyor.</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Standardize edilemedigi icin Faz 1 genel kapsayici skora alinmadi; business team ek kural tanimlamali.</t>
         </is>
       </c>
     </row>
